--- a/Raroc & Hurdle rate modelling.xlsx
+++ b/Raroc & Hurdle rate modelling.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/847fabfc857bf06b/Desktop/FRM/Projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="254" documentId="8_{7C031DAE-D7BD-4501-BBDC-04207F423434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A00A0A8D-3A70-4F3B-AF11-0ED6D266D37C}"/>
+  <xr:revisionPtr revIDLastSave="282" documentId="8_{7C031DAE-D7BD-4501-BBDC-04207F423434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96FD403F-43F4-4A9F-B2BF-6994CE02DC0B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{C3BF02C8-917C-451C-9EC5-3F8EAB8F37CE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
   <si>
     <t>Sl No:</t>
   </si>
@@ -90,9 +90,6 @@
   </si>
   <si>
     <t>Economic Capital</t>
-  </si>
-  <si>
-    <t>Risk Adjusted Return</t>
   </si>
   <si>
     <t>Total</t>
@@ -201,6 +198,15 @@
   </si>
   <si>
     <t>Formulas</t>
+  </si>
+  <si>
+    <t>Risk Adjusted Return before tax</t>
+  </si>
+  <si>
+    <t>Risk Adjusted Return after tax</t>
+  </si>
+  <si>
+    <t>Less: Tax @ 30%</t>
   </si>
 </sst>
 </file>
@@ -368,7 +374,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -391,15 +397,15 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -418,45 +424,46 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -479,10 +486,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -782,15 +785,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7F1723A-CBE6-4317-9304-5D3992232B20}">
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="47" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1" s="48" t="s">
         <v>1</v>
@@ -802,10 +805,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="49" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="51">
         <v>1</v>
       </c>
@@ -816,13 +819,14 @@
         <v>5.6981572052238846E-2</v>
       </c>
       <c r="D2" s="54">
-        <v>0.45</v>
+        <v>0.35169592564001417</v>
       </c>
       <c r="E2" s="53">
         <v>0.11575387118681511</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="55">
         <v>2</v>
       </c>
@@ -833,13 +837,14 @@
         <v>4.8475992244990246E-2</v>
       </c>
       <c r="D3" s="56">
-        <v>0.45</v>
+        <v>0.33903870304024408</v>
       </c>
       <c r="E3" s="53">
         <v>0.11992567153837734</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="55">
         <v>3</v>
       </c>
@@ -850,13 +855,14 @@
         <v>2.0339054746107373E-2</v>
       </c>
       <c r="D4" s="56">
-        <v>0.45</v>
+        <v>0.69064927587385094</v>
       </c>
       <c r="E4" s="53">
         <v>0.1258996155975704</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="55">
         <v>4</v>
       </c>
@@ -867,13 +873,14 @@
         <v>3.9190503311987583E-2</v>
       </c>
       <c r="D5" s="56">
-        <v>0.45</v>
+        <v>0.24844378273133538</v>
       </c>
       <c r="E5" s="53">
         <v>0.12382280882056158</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="55">
         <v>5</v>
       </c>
@@ -884,13 +891,14 @@
         <v>4.9807073686785178E-2</v>
       </c>
       <c r="D6" s="56">
-        <v>0.45</v>
+        <v>0.47692779861809298</v>
       </c>
       <c r="E6" s="53">
         <v>0.10149116017134595</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="55">
         <v>6</v>
       </c>
@@ -901,13 +909,14 @@
         <v>1.1442720759738789E-2</v>
       </c>
       <c r="D7" s="56">
-        <v>0.45</v>
+        <v>0.36116161253290635</v>
       </c>
       <c r="E7" s="53">
         <v>0.13136829682509321</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="55">
         <v>7</v>
       </c>
@@ -918,13 +927,14 @@
         <v>1.5967169097475607E-2</v>
       </c>
       <c r="D8" s="56">
-        <v>0.45</v>
+        <v>0.26492403810112031</v>
       </c>
       <c r="E8" s="53">
         <v>0.11144430099995281</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="55">
         <v>8</v>
       </c>
@@ -935,13 +945,14 @@
         <v>4.3499080806023334E-2</v>
       </c>
       <c r="D9" s="56">
-        <v>0.45</v>
+        <v>0.24926484699453844</v>
       </c>
       <c r="E9" s="53">
         <v>0.10761221472943579</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="55">
         <v>9</v>
       </c>
@@ -952,13 +963,14 @@
         <v>1.0114371015928644E-2</v>
       </c>
       <c r="D10" s="56">
-        <v>0.45</v>
+        <v>0.21409737444550792</v>
       </c>
       <c r="E10" s="53">
         <v>0.13082756582216057</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="55">
         <v>10</v>
       </c>
@@ -969,13 +981,14 @@
         <v>3.9033389150312611E-2</v>
       </c>
       <c r="D11" s="56">
-        <v>0.45</v>
+        <v>0.31568127025083792</v>
       </c>
       <c r="E11" s="53">
         <v>0.12959774672169735</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="55">
         <v>11</v>
       </c>
@@ -986,13 +999,14 @@
         <v>2.767369423126026E-2</v>
       </c>
       <c r="D12" s="56">
-        <v>0.45</v>
+        <v>0.44498065115823748</v>
       </c>
       <c r="E12" s="53">
         <v>0.10631616911340019</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="55">
         <v>12</v>
       </c>
@@ -1003,13 +1017,14 @@
         <v>4.9376226219418631E-2</v>
       </c>
       <c r="D13" s="56">
-        <v>0.45</v>
+        <v>0.32100408780730172</v>
       </c>
       <c r="E13" s="53">
         <v>0.13530221433811174</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="55">
         <v>13</v>
       </c>
@@ -1020,13 +1035,14 @@
         <v>1.1947323049418842E-2</v>
       </c>
       <c r="D14" s="56">
-        <v>0.45</v>
+        <v>0.61231089109667203</v>
       </c>
       <c r="E14" s="53">
         <v>0.11153450766439332</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="55">
         <v>14</v>
       </c>
@@ -1037,13 +1053,14 @@
         <v>3.7499439591030713E-2</v>
       </c>
       <c r="D15" s="56">
-        <v>0.45</v>
+        <v>0.66422676411838821</v>
       </c>
       <c r="E15" s="53">
         <v>0.11511567062925958</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="55">
         <v>15</v>
       </c>
@@ -1054,13 +1071,14 @@
         <v>1.1703109789367713E-2</v>
       </c>
       <c r="D16" s="56">
-        <v>0.45</v>
+        <v>0.23878214999183223</v>
       </c>
       <c r="E16" s="53">
         <v>0.11808511414556738</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="55">
         <v>16</v>
       </c>
@@ -1071,13 +1089,14 @@
         <v>2.1646145833825646E-2</v>
       </c>
       <c r="D17" s="56">
-        <v>0.45</v>
+        <v>0.6081541029929991</v>
       </c>
       <c r="E17" s="53">
         <v>0.10661531317065576</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="55">
         <v>17</v>
       </c>
@@ -1088,13 +1107,14 @@
         <v>5.1647988402246367E-2</v>
       </c>
       <c r="D18" s="56">
-        <v>0.45</v>
+        <v>0.32507606539887124</v>
       </c>
       <c r="E18" s="53">
         <v>0.13411748473133245</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="55">
         <v>18</v>
       </c>
@@ -1105,13 +1125,14 @@
         <v>2.2563764262680433E-2</v>
       </c>
       <c r="D19" s="56">
-        <v>0.45</v>
+        <v>0.57995192638740534</v>
       </c>
       <c r="E19" s="53">
         <v>0.13114761854443777</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="55">
         <v>19</v>
       </c>
@@ -1122,13 +1143,14 @@
         <v>5.1540412703311021E-2</v>
       </c>
       <c r="D20" s="56">
-        <v>0.45</v>
+        <v>0.56663508816453678</v>
       </c>
       <c r="E20" s="53">
         <v>0.12640377877847594</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F20" s="2"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="55">
         <v>20</v>
       </c>
@@ -1139,13 +1161,14 @@
         <v>4.33881166579283E-2</v>
       </c>
       <c r="D21" s="56">
-        <v>0.45</v>
+        <v>0.41513870386821605</v>
       </c>
       <c r="E21" s="53">
         <v>0.13166906135162915</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="55">
         <v>21</v>
       </c>
@@ -1156,13 +1179,14 @@
         <v>3.1561189455238316E-2</v>
       </c>
       <c r="D22" s="56">
-        <v>0.45</v>
+        <v>0.30486747389021596</v>
       </c>
       <c r="E22" s="53">
         <v>0.1228330485075699</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F22" s="2"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="55">
         <v>22</v>
       </c>
@@ -1173,13 +1197,14 @@
         <v>3.4485471405317374E-2</v>
       </c>
       <c r="D23" s="56">
-        <v>0.45</v>
+        <v>0.403886053990132</v>
       </c>
       <c r="E23" s="53">
         <v>0.12230930393251914</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="55">
         <v>23</v>
       </c>
@@ -1190,13 +1215,14 @@
         <v>5.1173143042301278E-2</v>
       </c>
       <c r="D24" s="56">
-        <v>0.45</v>
+        <v>0.45547307616928723</v>
       </c>
       <c r="E24" s="53">
         <v>0.13041365348042736</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="55">
         <v>24</v>
       </c>
@@ -1207,13 +1233,14 @@
         <v>5.0923398407887212E-2</v>
       </c>
       <c r="D25" s="56">
-        <v>0.45</v>
+        <v>0.23046413256599207</v>
       </c>
       <c r="E25" s="53">
         <v>0.11107683341940311</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F25" s="2"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="55">
         <v>25</v>
       </c>
@@ -1224,13 +1251,14 @@
         <v>1.0333077966292938E-2</v>
       </c>
       <c r="D26" s="56">
-        <v>0.45</v>
+        <v>0.49094368618115669</v>
       </c>
       <c r="E26" s="53">
         <v>0.12617227938457928</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F26" s="2"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="55">
         <v>26</v>
       </c>
@@ -1241,13 +1269,14 @@
         <v>5.5289399739773384E-2</v>
       </c>
       <c r="D27" s="56">
-        <v>0.45</v>
+        <v>0.25692441508306896</v>
       </c>
       <c r="E27" s="53">
         <v>0.10857832731223976</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F27" s="2"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="55">
         <v>27</v>
       </c>
@@ -1258,13 +1287,14 @@
         <v>1.3568750867256852E-2</v>
       </c>
       <c r="D28" s="56">
-        <v>0.45</v>
+        <v>0.6633103429721009</v>
       </c>
       <c r="E28" s="53">
         <v>0.13792462494892924</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F28" s="2"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="55">
         <v>28</v>
       </c>
@@ -1275,13 +1305,14 @@
         <v>2.5097972684428302E-2</v>
       </c>
       <c r="D29" s="56">
-        <v>0.45</v>
+        <v>0.24368356601692198</v>
       </c>
       <c r="E29" s="53">
         <v>0.10762410425801257</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F29" s="2"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="55">
         <v>29</v>
       </c>
@@ -1292,13 +1323,14 @@
         <v>5.2469387805803167E-2</v>
       </c>
       <c r="D30" s="56">
-        <v>0.45</v>
+        <v>0.56505132067971264</v>
       </c>
       <c r="E30" s="53">
         <v>0.10164171729242658</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F30" s="2"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="55">
         <v>30</v>
       </c>
@@ -1309,13 +1341,14 @@
         <v>5.6651472614051054E-2</v>
       </c>
       <c r="D31" s="56">
-        <v>0.45</v>
+        <v>0.4722905932909065</v>
       </c>
       <c r="E31" s="53">
         <v>0.1045533625918828</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F31" s="2"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="55">
         <v>31</v>
       </c>
@@ -1326,13 +1359,14 @@
         <v>3.0565378751610764E-2</v>
       </c>
       <c r="D32" s="56">
-        <v>0.45</v>
+        <v>0.63461637672113402</v>
       </c>
       <c r="E32" s="53">
         <v>0.11643396080613838</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F32" s="2"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="55">
         <v>32</v>
       </c>
@@ -1343,13 +1377,14 @@
         <v>5.3612601656484307E-2</v>
       </c>
       <c r="D33" s="56">
-        <v>0.45</v>
+        <v>0.26427613870425681</v>
       </c>
       <c r="E33" s="53">
         <v>0.13167972715536744</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F33" s="2"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="55">
         <v>33</v>
       </c>
@@ -1360,13 +1395,14 @@
         <v>1.2662826088776969E-2</v>
       </c>
       <c r="D34" s="56">
-        <v>0.45</v>
+        <v>0.62262389971490506</v>
       </c>
       <c r="E34" s="53">
         <v>0.12924134718435398</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F34" s="2"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="55">
         <v>34</v>
       </c>
@@ -1377,13 +1413,14 @@
         <v>1.0169743635614443E-2</v>
       </c>
       <c r="D35" s="56">
-        <v>0.45</v>
+        <v>0.68983689975407003</v>
       </c>
       <c r="E35" s="53">
         <v>0.13468678970889267</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F35" s="2"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="55">
         <v>35</v>
       </c>
@@ -1394,13 +1431,14 @@
         <v>3.0055523740202525E-2</v>
       </c>
       <c r="D36" s="56">
-        <v>0.45</v>
+        <v>0.5300793531943534</v>
       </c>
       <c r="E36" s="53">
         <v>0.13361619331255495</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F36" s="2"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="55">
         <v>36</v>
       </c>
@@ -1411,13 +1449,14 @@
         <v>4.8454472836271259E-2</v>
       </c>
       <c r="D37" s="56">
-        <v>0.45</v>
+        <v>0.59785757576352738</v>
       </c>
       <c r="E37" s="53">
         <v>0.12058224480445412</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F37" s="2"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="55">
         <v>37</v>
       </c>
@@ -1428,13 +1467,14 @@
         <v>5.1910534861334505E-2</v>
       </c>
       <c r="D38" s="56">
-        <v>0.45</v>
+        <v>0.23975885554750409</v>
       </c>
       <c r="E38" s="53">
         <v>0.13844756624017682</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F38" s="2"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="55">
         <v>38</v>
       </c>
@@ -1445,13 +1485,14 @@
         <v>5.3613842072692874E-2</v>
       </c>
       <c r="D39" s="56">
-        <v>0.45</v>
+        <v>0.59498578725052254</v>
       </c>
       <c r="E39" s="53">
         <v>0.11327921799175336</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F39" s="2"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="55">
         <v>39</v>
       </c>
@@ -1462,13 +1503,14 @@
         <v>3.2505942566761169E-2</v>
       </c>
       <c r="D40" s="56">
-        <v>0.45</v>
+        <v>0.60117178113189695</v>
       </c>
       <c r="E40" s="53">
         <v>0.13051528551717331</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F40" s="2"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="55">
         <v>40</v>
       </c>
@@ -1479,13 +1521,14 @@
         <v>4.3424758897292831E-2</v>
       </c>
       <c r="D41" s="56">
-        <v>0.45</v>
+        <v>0.64678015251833931</v>
       </c>
       <c r="E41" s="53">
         <v>0.10584484207039921</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F41" s="2"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="55">
         <v>41</v>
       </c>
@@ -1496,13 +1539,14 @@
         <v>4.7348815314400321E-2</v>
       </c>
       <c r="D42" s="56">
-        <v>0.45</v>
+        <v>0.29802319506158736</v>
       </c>
       <c r="E42" s="53">
         <v>0.11377772708864226</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F42" s="2"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="55">
         <v>42</v>
       </c>
@@ -1513,13 +1557,14 @@
         <v>1.3674280994419225E-2</v>
       </c>
       <c r="D43" s="56">
-        <v>0.45</v>
+        <v>0.27041723174687338</v>
       </c>
       <c r="E43" s="53">
         <v>0.11012062410619328</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F43" s="2"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="55">
         <v>43</v>
       </c>
@@ -1530,13 +1575,14 @@
         <v>5.676202379632414E-2</v>
       </c>
       <c r="D44" s="56">
-        <v>0.45</v>
+        <v>0.46055551204184697</v>
       </c>
       <c r="E44" s="53">
         <v>0.13868641965705727</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F44" s="2"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="55">
         <v>44</v>
       </c>
@@ -1547,13 +1593,14 @@
         <v>3.6418290708041159E-2</v>
       </c>
       <c r="D45" s="56">
-        <v>0.45</v>
+        <v>0.63229804231588249</v>
       </c>
       <c r="E45" s="53">
         <v>0.11512292188103702</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F45" s="2"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="55">
         <v>45</v>
       </c>
@@ -1564,13 +1611,14 @@
         <v>3.795859199446161E-2</v>
       </c>
       <c r="D46" s="56">
-        <v>0.45</v>
+        <v>0.28290816055339119</v>
       </c>
       <c r="E46" s="53">
         <v>0.11908913202543403</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F46" s="2"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="55">
         <v>46</v>
       </c>
@@ -1581,13 +1629,14 @@
         <v>4.0418583064794865E-2</v>
       </c>
       <c r="D47" s="56">
-        <v>0.45</v>
+        <v>0.44450404250639997</v>
       </c>
       <c r="E47" s="53">
         <v>0.12412602058290595</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F47" s="2"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="55">
         <v>47</v>
       </c>
@@ -1598,13 +1647,14 @@
         <v>4.1871553647260272E-2</v>
       </c>
       <c r="D48" s="56">
-        <v>0.45</v>
+        <v>0.31914538221676392</v>
       </c>
       <c r="E48" s="53">
         <v>0.10127489691999735</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F48" s="2"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="55">
         <v>48</v>
       </c>
@@ -1615,13 +1665,14 @@
         <v>4.3646293932275725E-2</v>
       </c>
       <c r="D49" s="56">
-        <v>0.45</v>
+        <v>0.29875486333017853</v>
       </c>
       <c r="E49" s="53">
         <v>0.12239370289672052</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F49" s="2"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="55">
         <v>49</v>
       </c>
@@ -1632,13 +1683,14 @@
         <v>4.5988347961935357E-2</v>
       </c>
       <c r="D50" s="56">
-        <v>0.45</v>
+        <v>0.68617424011340833</v>
       </c>
       <c r="E50" s="53">
         <v>0.10075484023360672</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F50" s="2"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="55">
         <v>50</v>
       </c>
@@ -1649,13 +1701,14 @@
         <v>5.8158710199308669E-2</v>
       </c>
       <c r="D51" s="56">
-        <v>0.45</v>
+        <v>0.47821276883639796</v>
       </c>
       <c r="E51" s="53">
         <v>0.10866445438751544</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F51" s="2"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="55">
         <v>51</v>
       </c>
@@ -1666,13 +1719,14 @@
         <v>2.1663832222160669E-2</v>
       </c>
       <c r="D52" s="56">
-        <v>0.45</v>
+        <v>0.37728556210490194</v>
       </c>
       <c r="E52" s="53">
         <v>0.11806101871030746</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F52" s="2"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="55">
         <v>52</v>
       </c>
@@ -1683,13 +1737,14 @@
         <v>2.996236509505823E-2</v>
       </c>
       <c r="D53" s="56">
-        <v>0.45</v>
+        <v>0.61104187246048813</v>
       </c>
       <c r="E53" s="53">
         <v>0.10725827034040378</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F53" s="2"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="55">
         <v>53</v>
       </c>
@@ -1700,13 +1755,14 @@
         <v>2.8207052284732879E-2</v>
       </c>
       <c r="D54" s="56">
-        <v>0.45</v>
+        <v>0.24488742906452443</v>
       </c>
       <c r="E54" s="53">
         <v>0.10642642368353039</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F54" s="2"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="55">
         <v>54</v>
       </c>
@@ -1717,13 +1773,14 @@
         <v>3.2130693570795996E-2</v>
       </c>
       <c r="D55" s="56">
-        <v>0.45</v>
+        <v>0.25464974174436694</v>
       </c>
       <c r="E55" s="53">
         <v>0.10250278832607154</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F55" s="2"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="55">
         <v>55</v>
       </c>
@@ -1734,13 +1791,14 @@
         <v>2.441100327085248E-2</v>
       </c>
       <c r="D56" s="56">
-        <v>0.45</v>
+        <v>0.30861886504360347</v>
       </c>
       <c r="E56" s="53">
         <v>0.10137775178807033</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F56" s="2"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="55">
         <v>56</v>
       </c>
@@ -1751,13 +1809,14 @@
         <v>5.3328414198889326E-2</v>
       </c>
       <c r="D57" s="56">
-        <v>0.45</v>
+        <v>0.34290007437103986</v>
       </c>
       <c r="E57" s="53">
         <v>0.10072910356217013</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F57" s="2"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="55">
         <v>57</v>
       </c>
@@ -1768,13 +1827,14 @@
         <v>5.5072206066467781E-2</v>
       </c>
       <c r="D58" s="56">
-        <v>0.45</v>
+        <v>0.33976200731732742</v>
       </c>
       <c r="E58" s="53">
         <v>0.10125367629307698</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F58" s="2"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="55">
         <v>58</v>
       </c>
@@ -1785,13 +1845,14 @@
         <v>3.9478714859582362E-2</v>
       </c>
       <c r="D59" s="56">
-        <v>0.45</v>
+        <v>0.3213960702055253</v>
       </c>
       <c r="E59" s="53">
         <v>0.13995251362072786</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F59" s="2"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="55">
         <v>59</v>
       </c>
@@ -1802,13 +1863,14 @@
         <v>2.9011169908627489E-2</v>
       </c>
       <c r="D60" s="56">
-        <v>0.45</v>
+        <v>0.4221139839134509</v>
       </c>
       <c r="E60" s="53">
         <v>0.13433242675583779</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F60" s="2"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="55">
         <v>60</v>
       </c>
@@ -1819,13 +1881,14 @@
         <v>1.1732376427232622E-2</v>
       </c>
       <c r="D61" s="56">
-        <v>0.45</v>
+        <v>0.2117527587759801</v>
       </c>
       <c r="E61" s="53">
         <v>0.10031872765066355</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F61" s="2"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="55">
         <v>61</v>
       </c>
@@ -1836,13 +1899,14 @@
         <v>1.0611659424387423E-2</v>
       </c>
       <c r="D62" s="56">
-        <v>0.45</v>
+        <v>0.68773675939844758</v>
       </c>
       <c r="E62" s="53">
         <v>0.12708290028875185</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F62" s="2"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="55">
         <v>62</v>
       </c>
@@ -1853,13 +1917,14 @@
         <v>2.1458863144407495E-2</v>
       </c>
       <c r="D63" s="56">
-        <v>0.45</v>
+        <v>0.39674587505405601</v>
       </c>
       <c r="E63" s="53">
         <v>0.12142183819903039</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F63" s="2"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="55">
         <v>63</v>
       </c>
@@ -1870,13 +1935,14 @@
         <v>2.3410762736715891E-2</v>
       </c>
       <c r="D64" s="56">
-        <v>0.45</v>
+        <v>0.42137740161448733</v>
       </c>
       <c r="E64" s="53">
         <v>0.10281574852737184</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F64" s="2"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="55">
         <v>64</v>
       </c>
@@ -1887,13 +1953,14 @@
         <v>2.333808157823301E-2</v>
       </c>
       <c r="D65" s="56">
-        <v>0.45</v>
+        <v>0.29064867434225439</v>
       </c>
       <c r="E65" s="53">
         <v>0.10440602577013545</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F65" s="2"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="55">
         <v>65</v>
       </c>
@@ -1904,13 +1971,14 @@
         <v>1.1950136557084717E-2</v>
       </c>
       <c r="D66" s="56">
-        <v>0.45</v>
+        <v>0.54348701272375433</v>
       </c>
       <c r="E66" s="53">
         <v>0.13511970343324797</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F66" s="2"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="55">
         <v>66</v>
       </c>
@@ -1921,13 +1989,14 @@
         <v>5.8269265206104433E-2</v>
       </c>
       <c r="D67" s="56">
-        <v>0.45</v>
+        <v>0.60731939550287373</v>
       </c>
       <c r="E67" s="53">
         <v>0.10265356627612908</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F67" s="2"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="55">
         <v>67</v>
       </c>
@@ -1938,13 +2007,14 @@
         <v>4.2326681377969522E-2</v>
       </c>
       <c r="D68" s="56">
-        <v>0.45</v>
+        <v>0.54733973209912379</v>
       </c>
       <c r="E68" s="53">
         <v>0.10495585022121799</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F68" s="2"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="55">
         <v>68</v>
       </c>
@@ -1955,13 +2025,14 @@
         <v>2.0607417482393933E-2</v>
       </c>
       <c r="D69" s="56">
-        <v>0.45</v>
+        <v>0.31161773195781539</v>
       </c>
       <c r="E69" s="53">
         <v>0.1152097850178625</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F69" s="2"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="55">
         <v>69</v>
       </c>
@@ -1972,13 +2043,14 @@
         <v>5.5943242813198658E-2</v>
       </c>
       <c r="D70" s="56">
-        <v>0.45</v>
+        <v>0.65960207770955959</v>
       </c>
       <c r="E70" s="53">
         <v>0.10438510330015383</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F70" s="2"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="55">
         <v>70</v>
       </c>
@@ -1989,13 +2061,14 @@
         <v>1.4203439875536579E-2</v>
       </c>
       <c r="D71" s="56">
-        <v>0.45</v>
+        <v>0.44582121139090425</v>
       </c>
       <c r="E71" s="53">
         <v>0.10509648265241604</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F71" s="2"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="55">
         <v>71</v>
       </c>
@@ -2006,13 +2079,14 @@
         <v>4.3920475820826387E-2</v>
       </c>
       <c r="D72" s="56">
-        <v>0.45</v>
+        <v>0.46300614450734534</v>
       </c>
       <c r="E72" s="53">
         <v>0.1388599163158494</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F72" s="2"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="55">
         <v>72</v>
       </c>
@@ -2023,13 +2097,14 @@
         <v>3.5737095870318626E-2</v>
       </c>
       <c r="D73" s="56">
-        <v>0.45</v>
+        <v>0.36469003508983466</v>
       </c>
       <c r="E73" s="53">
         <v>0.13511956428642136</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F73" s="2"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="55">
         <v>73</v>
       </c>
@@ -2040,13 +2115,14 @@
         <v>3.9974862484740449E-2</v>
       </c>
       <c r="D74" s="56">
-        <v>0.45</v>
+        <v>0.44641921040529908</v>
       </c>
       <c r="E74" s="53">
         <v>0.10026099477580827</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F74" s="2"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="55">
         <v>74</v>
       </c>
@@ -2057,13 +2133,14 @@
         <v>1.2279061281115403E-2</v>
       </c>
       <c r="D75" s="56">
-        <v>0.45</v>
+        <v>0.4899126991343784</v>
       </c>
       <c r="E75" s="53">
         <v>0.11074412352754875</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F75" s="2"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="55">
         <v>75</v>
       </c>
@@ -2074,13 +2151,14 @@
         <v>4.3680320905037082E-2</v>
       </c>
       <c r="D76" s="56">
-        <v>0.45</v>
+        <v>0.6128320693544691</v>
       </c>
       <c r="E76" s="53">
         <v>0.13623491948657335</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F76" s="2"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="55">
         <v>76</v>
       </c>
@@ -2091,13 +2169,14 @@
         <v>3.9221079323609319E-2</v>
       </c>
       <c r="D77" s="56">
-        <v>0.45</v>
+        <v>0.55158045878683415</v>
       </c>
       <c r="E77" s="53">
         <v>0.10551854286332567</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F77" s="2"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="55">
         <v>77</v>
       </c>
@@ -2108,13 +2187,14 @@
         <v>5.3480651284804309E-2</v>
       </c>
       <c r="D78" s="56">
-        <v>0.45</v>
+        <v>0.22903941923322435</v>
       </c>
       <c r="E78" s="53">
         <v>0.1011601167988487</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F78" s="2"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="55">
         <v>78</v>
       </c>
@@ -2125,13 +2205,14 @@
         <v>1.0870188362631901E-2</v>
       </c>
       <c r="D79" s="56">
-        <v>0.45</v>
+        <v>0.2246684297905045</v>
       </c>
       <c r="E79" s="53">
         <v>0.12164701366846634</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F79" s="2"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="55">
         <v>79</v>
       </c>
@@ -2142,13 +2223,14 @@
         <v>2.4968299520919099E-2</v>
       </c>
       <c r="D80" s="56">
-        <v>0.45</v>
+        <v>0.69029541274852779</v>
       </c>
       <c r="E80" s="53">
         <v>0.11933072113471194</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F80" s="2"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="55">
         <v>80</v>
       </c>
@@ -2159,13 +2241,14 @@
         <v>3.5662444226601267E-2</v>
       </c>
       <c r="D81" s="56">
-        <v>0.45</v>
+        <v>0.33517539806233332</v>
       </c>
       <c r="E81" s="53">
         <v>0.13237319550437771</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F81" s="2"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="55">
         <v>81</v>
       </c>
@@ -2176,13 +2259,14 @@
         <v>2.6967058719719314E-2</v>
       </c>
       <c r="D82" s="56">
-        <v>0.45</v>
+        <v>0.65168796537799534</v>
       </c>
       <c r="E82" s="53">
         <v>0.10067927682232317</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F82" s="2"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="55">
         <v>82</v>
       </c>
@@ -2193,13 +2277,14 @@
         <v>1.8815576231867477E-2</v>
       </c>
       <c r="D83" s="56">
-        <v>0.45</v>
+        <v>0.65605080246849312</v>
       </c>
       <c r="E83" s="53">
         <v>0.13973602197883542</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F83" s="2"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="55">
         <v>83</v>
       </c>
@@ -2210,13 +2295,14 @@
         <v>3.2925012514916363E-2</v>
       </c>
       <c r="D84" s="56">
-        <v>0.45</v>
+        <v>0.34616762559222491</v>
       </c>
       <c r="E84" s="53">
         <v>0.1320235067564923</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F84" s="2"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="55">
         <v>84</v>
       </c>
@@ -2227,13 +2313,14 @@
         <v>2.0879036035778949E-2</v>
       </c>
       <c r="D85" s="56">
-        <v>0.45</v>
+        <v>0.66212402721431252</v>
       </c>
       <c r="E85" s="53">
         <v>0.10002649397962075</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F85" s="2"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="55">
         <v>85</v>
       </c>
@@ -2244,13 +2331,14 @@
         <v>5.0851557829304547E-2</v>
       </c>
       <c r="D86" s="56">
-        <v>0.45</v>
+        <v>0.34106067816254171</v>
       </c>
       <c r="E86" s="53">
         <v>0.13538012546279188</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F86" s="2"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="55">
         <v>86</v>
       </c>
@@ -2261,13 +2349,14 @@
         <v>5.7702934543936872E-2</v>
       </c>
       <c r="D87" s="56">
-        <v>0.45</v>
+        <v>0.42962505681095808</v>
       </c>
       <c r="E87" s="53">
         <v>0.10980279635119557</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F87" s="2"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="55">
         <v>87</v>
       </c>
@@ -2278,13 +2367,14 @@
         <v>3.0008868947872594E-2</v>
       </c>
       <c r="D88" s="56">
-        <v>0.45</v>
+        <v>0.42656939327163235</v>
       </c>
       <c r="E88" s="53">
         <v>0.13196662285067839</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F88" s="2"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="55">
         <v>88</v>
       </c>
@@ -2295,13 +2385,14 @@
         <v>5.7983949502188034E-2</v>
       </c>
       <c r="D89" s="56">
-        <v>0.45</v>
+        <v>0.24529615989531661</v>
       </c>
       <c r="E89" s="53">
         <v>0.12244750285210446</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F89" s="2"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="55">
         <v>89</v>
       </c>
@@ -2312,13 +2403,14 @@
         <v>5.2498773572615759E-2</v>
       </c>
       <c r="D90" s="56">
-        <v>0.45</v>
+        <v>0.47841175237598021</v>
       </c>
       <c r="E90" s="53">
         <v>0.12336372117124106</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F90" s="2"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="55">
         <v>90</v>
       </c>
@@ -2329,13 +2421,14 @@
         <v>1.2635764473106336E-2</v>
       </c>
       <c r="D91" s="56">
-        <v>0.45</v>
+        <v>0.5404282094171039</v>
       </c>
       <c r="E91" s="53">
         <v>0.10524266478295946</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F91" s="2"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="55">
         <v>91</v>
       </c>
@@ -2346,13 +2439,14 @@
         <v>1.3085501551217717E-2</v>
       </c>
       <c r="D92" s="56">
-        <v>0.45</v>
+        <v>0.36883666172921803</v>
       </c>
       <c r="E92" s="53">
         <v>0.10142017238805404</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F92" s="2"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="55">
         <v>92</v>
       </c>
@@ -2363,13 +2457,14 @@
         <v>4.9845548787286774E-2</v>
       </c>
       <c r="D93" s="56">
-        <v>0.45</v>
+        <v>0.69111517152179447</v>
       </c>
       <c r="E93" s="53">
         <v>0.11020493789417668</v>
       </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F93" s="2"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="55">
         <v>93</v>
       </c>
@@ -2380,13 +2475,14 @@
         <v>5.0411256926503542E-2</v>
       </c>
       <c r="D94" s="56">
-        <v>0.45</v>
+        <v>0.60933843535586474</v>
       </c>
       <c r="E94" s="53">
         <v>0.13124098152613256</v>
       </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F94" s="2"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="55">
         <v>94</v>
       </c>
@@ -2397,13 +2493,14 @@
         <v>5.8145477038991644E-2</v>
       </c>
       <c r="D95" s="56">
-        <v>0.45</v>
+        <v>0.47619805291810435</v>
       </c>
       <c r="E95" s="53">
         <v>0.11979545083685306</v>
       </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F95" s="2"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="55">
         <v>95</v>
       </c>
@@ -2414,13 +2511,14 @@
         <v>3.2572506188292945E-2</v>
       </c>
       <c r="D96" s="56">
-        <v>0.45</v>
+        <v>0.44802418381057518</v>
       </c>
       <c r="E96" s="53">
         <v>0.13526842062904687</v>
       </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F96" s="2"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="55">
         <v>96</v>
       </c>
@@ -2431,13 +2529,14 @@
         <v>5.2432685396596533E-2</v>
       </c>
       <c r="D97" s="56">
-        <v>0.45</v>
+        <v>0.27749968198730535</v>
       </c>
       <c r="E97" s="53">
         <v>0.11665115624996511</v>
       </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F97" s="2"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="55">
         <v>97</v>
       </c>
@@ -2448,13 +2547,14 @@
         <v>4.4779252151959749E-2</v>
       </c>
       <c r="D98" s="56">
-        <v>0.45</v>
+        <v>0.42073014950101695</v>
       </c>
       <c r="E98" s="53">
         <v>0.13421198420795918</v>
       </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F98" s="2"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="55">
         <v>98</v>
       </c>
@@ -2465,13 +2565,14 @@
         <v>5.1115027311982954E-2</v>
       </c>
       <c r="D99" s="56">
-        <v>0.45</v>
+        <v>0.67895755809370006</v>
       </c>
       <c r="E99" s="53">
         <v>0.11310563310437757</v>
       </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F99" s="2"/>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="55">
         <v>99</v>
       </c>
@@ -2482,13 +2583,14 @@
         <v>2.96340928516063E-2</v>
       </c>
       <c r="D100" s="56">
-        <v>0.45</v>
+        <v>0.62216876669906396</v>
       </c>
       <c r="E100" s="53">
         <v>0.11477011468572759</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F100" s="2"/>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="57">
         <v>100</v>
       </c>
@@ -2499,11 +2601,12 @@
         <v>4.5849843442694431E-2</v>
       </c>
       <c r="D101" s="59">
-        <v>0.45</v>
+        <v>0.62765712114478645</v>
       </c>
       <c r="E101" s="58">
         <v>0.12479544093419508</v>
       </c>
+      <c r="F101" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2533,22 +2636,22 @@
         <v>4</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="11"/>
       <c r="B2" s="12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="12" t="s">
-        <v>29</v>
-      </c>
       <c r="L2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -2568,7 +2671,7 @@
         <v>2.9575156577117152</v>
       </c>
       <c r="L3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -2576,7 +2679,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C4" s="16">
         <f>+AVERAGE('2. Working sheet'!C10:C109)</f>
@@ -2587,7 +2690,7 @@
         <v>1.5427860655273573E-2</v>
       </c>
       <c r="L4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
@@ -2595,21 +2698,21 @@
         <v>3</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C5" s="18">
         <f>+AVERAGE('2. Working sheet'!D10:D109)</f>
-        <v>0.4500000000000004</v>
+        <v>0.44719690946330865</v>
       </c>
       <c r="D5" s="17">
         <f>+_xlfn.STDEV.P('2. Working sheet'!D10:D109)</f>
-        <v>3.8857805861880479E-16</v>
+        <v>0.15144768800087066</v>
       </c>
     </row>
     <row r="7" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="8">
         <f>SUM(B10:B109)</f>
@@ -2617,11 +2720,11 @@
       </c>
       <c r="E8" s="8">
         <f>SUM(E10:E109)</f>
-        <v>9.1356316019026256</v>
+        <v>9.007556776357184</v>
       </c>
       <c r="H8" s="8">
         <f>SUM(H10:H109)</f>
-        <v>46.739626286012999</v>
+        <v>49.369272813376611</v>
       </c>
       <c r="J8" s="8">
         <f>SUM(J10:J109)</f>
@@ -2635,16 +2738,16 @@
         <v>0</v>
       </c>
       <c r="B9" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="D9" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="12" t="s">
-        <v>37</v>
-      </c>
       <c r="E9" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>5</v>
@@ -2653,13 +2756,13 @@
         <v>6</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I9" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="J9" s="19" t="s">
         <v>38</v>
-      </c>
-      <c r="J9" s="19" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
@@ -2676,11 +2779,11 @@
       </c>
       <c r="D10" s="26">
         <f>+'1. Portfolio Detail'!D2</f>
-        <v>0.45</v>
+        <v>0.35169592564001417</v>
       </c>
       <c r="E10" s="36">
         <f>+B10*C10*D10</f>
-        <v>5.4138438108529863E-2</v>
+        <v>4.2311706896186727E-2</v>
       </c>
       <c r="F10" s="29">
         <f>+C10*(1-C10)</f>
@@ -2688,11 +2791,11 @@
       </c>
       <c r="G10" s="37">
         <f>+(D10-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>9.1204379112171524E-3</v>
       </c>
       <c r="H10" s="32">
         <f>+B10*(SQRT((C10*G10)+((D10^2)*F10)))</f>
-        <v>0.22024121723331555</v>
+        <v>0.17873163190992891</v>
       </c>
       <c r="I10" s="38">
         <f>+'1. Portfolio Detail'!E2</f>
@@ -2718,11 +2821,11 @@
       </c>
       <c r="D11" s="27">
         <f>+'1. Portfolio Detail'!D3</f>
-        <v>0.45</v>
+        <v>0.33903870304024408</v>
       </c>
       <c r="E11" s="40">
         <f t="shared" ref="E11:E74" si="1">+B11*C11*D11</f>
-        <v>0.11559485547699554</v>
+        <v>8.7091399731211147E-2</v>
       </c>
       <c r="F11" s="30">
         <f t="shared" ref="F11:F74" si="2">+C11*(1-C11)</f>
@@ -2730,11 +2833,11 @@
       </c>
       <c r="G11" s="41">
         <f>+(D11-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>1.1698197616654244E-2</v>
       </c>
       <c r="H11" s="33">
         <f t="shared" ref="H11:H74" si="3">+B11*(SQRT((C11*G11)+((D11^2)*F11)))</f>
-        <v>0.51213567303779328</v>
+        <v>0.405963280931883</v>
       </c>
       <c r="I11" s="42">
         <f>+'1. Portfolio Detail'!E3</f>
@@ -2760,11 +2863,11 @@
       </c>
       <c r="D12" s="27">
         <f>+'1. Portfolio Detail'!D4</f>
-        <v>0.45</v>
+        <v>0.69064927587385094</v>
       </c>
       <c r="E12" s="40">
         <f t="shared" si="1"/>
-        <v>7.0095747427269678E-2</v>
+        <v>0.10758128267217812</v>
       </c>
       <c r="F12" s="30">
         <f t="shared" si="2"/>
@@ -2772,11 +2875,11 @@
       </c>
       <c r="G12" s="41">
         <f>+(D12-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>5.9269054710892943E-2</v>
       </c>
       <c r="H12" s="33">
         <f t="shared" si="3"/>
-        <v>0.48647909872749195</v>
+        <v>0.79257301666576141</v>
       </c>
       <c r="I12" s="42">
         <f>+'1. Portfolio Detail'!E4</f>
@@ -2802,11 +2905,11 @@
       </c>
       <c r="D13" s="27">
         <f>+'1. Portfolio Detail'!D5</f>
-        <v>0.45</v>
+        <v>0.24844378273133538</v>
       </c>
       <c r="E13" s="40">
         <f t="shared" si="1"/>
-        <v>0.17703846267837053</v>
+        <v>9.7742456348343817E-2</v>
       </c>
       <c r="F13" s="30">
         <f t="shared" si="2"/>
@@ -2814,11 +2917,11 @@
       </c>
       <c r="G13" s="41">
         <f>+(D13-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>3.9502805385735827E-2</v>
       </c>
       <c r="H13" s="33">
         <f t="shared" si="3"/>
-        <v>0.87658866930217039</v>
+        <v>0.62468488124049648</v>
       </c>
       <c r="I13" s="42">
         <f>+'1. Portfolio Detail'!E5</f>
@@ -2844,11 +2947,11 @@
       </c>
       <c r="D14" s="27">
         <f>+'1. Portfolio Detail'!D6</f>
-        <v>0.45</v>
+        <v>0.47692779861809298</v>
       </c>
       <c r="E14" s="40">
         <f t="shared" si="1"/>
-        <v>7.5812552522909069E-2</v>
+        <v>8.0349141738599056E-2</v>
       </c>
       <c r="F14" s="30">
         <f t="shared" si="2"/>
@@ -2856,11 +2959,11 @@
       </c>
       <c r="G14" s="41">
         <f>+(D14-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>8.839257699340728E-4</v>
       </c>
       <c r="H14" s="33">
         <f t="shared" si="3"/>
-        <v>0.33113226699587317</v>
+        <v>0.35166398755993628</v>
       </c>
       <c r="I14" s="42">
         <f>+'1. Portfolio Detail'!E6</f>
@@ -2886,11 +2989,11 @@
       </c>
       <c r="D15" s="27">
         <f>+'1. Portfolio Detail'!D7</f>
-        <v>0.45</v>
+        <v>0.36116161253290635</v>
       </c>
       <c r="E15" s="40">
         <f t="shared" si="1"/>
-        <v>1.8007874521074534E-2</v>
+        <v>1.4452784445158927E-2</v>
       </c>
       <c r="F15" s="30">
         <f t="shared" si="2"/>
@@ -2898,11 +3001,11 @@
       </c>
       <c r="G15" s="41">
         <f>+(D15-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>7.4020723179024908E-3</v>
       </c>
       <c r="H15" s="33">
         <f t="shared" si="3"/>
-        <v>0.16737813525199247</v>
+        <v>0.13813649634939254</v>
       </c>
       <c r="I15" s="42">
         <f>+'1. Portfolio Detail'!E7</f>
@@ -2928,11 +3031,11 @@
       </c>
       <c r="D16" s="27">
         <f>+'1. Portfolio Detail'!D8</f>
-        <v>0.45</v>
+        <v>0.26492403810112031</v>
       </c>
       <c r="E16" s="40">
         <f t="shared" si="1"/>
-        <v>4.2006918533271202E-2</v>
+        <v>2.4730316635597771E-2</v>
       </c>
       <c r="F16" s="30">
         <f t="shared" si="2"/>
@@ -2940,11 +3043,11 @@
       </c>
       <c r="G16" s="41">
         <f>+(D16-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>3.322339963461686E-2</v>
       </c>
       <c r="H16" s="33">
         <f t="shared" si="3"/>
-        <v>0.32977038885891641</v>
+        <v>0.23626838763799471</v>
       </c>
       <c r="I16" s="42">
         <f>+'1. Portfolio Detail'!E8</f>
@@ -2970,11 +3073,11 @@
       </c>
       <c r="D17" s="27">
         <f>+'1. Portfolio Detail'!D9</f>
-        <v>0.45</v>
+        <v>0.24926484699453844</v>
       </c>
       <c r="E17" s="40">
         <f t="shared" si="1"/>
-        <v>0.15603078651245192</v>
+        <v>8.6428866947697372E-2</v>
       </c>
       <c r="F17" s="30">
         <f t="shared" si="2"/>
@@ -2982,11 +3085,11 @@
       </c>
       <c r="G17" s="41">
         <f>+(D17-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>3.9177101353141154E-2</v>
       </c>
       <c r="H17" s="33">
         <f t="shared" si="3"/>
-        <v>0.7316661338871342</v>
+        <v>0.52205031533027613</v>
       </c>
       <c r="I17" s="42">
         <f>+'1. Portfolio Detail'!E9</f>
@@ -3012,11 +3115,11 @@
       </c>
       <c r="D18" s="27">
         <f>+'1. Portfolio Detail'!D10</f>
-        <v>0.45</v>
+        <v>0.21409737444550792</v>
       </c>
       <c r="E18" s="40">
         <f t="shared" si="1"/>
-        <v>3.6896758717330023E-2</v>
+        <v>1.7554442593177254E-2</v>
       </c>
       <c r="F18" s="30">
         <f t="shared" si="2"/>
@@ -3024,11 +3127,11 @@
       </c>
       <c r="G18" s="41">
         <f>+(D18-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>5.4335393225514908E-2</v>
       </c>
       <c r="H18" s="33">
         <f t="shared" si="3"/>
-        <v>0.36501548230037206</v>
+        <v>0.25743906148708501</v>
       </c>
       <c r="I18" s="42">
         <f>+'1. Portfolio Detail'!E10</f>
@@ -3054,11 +3157,11 @@
       </c>
       <c r="D19" s="27">
         <f>+'1. Portfolio Detail'!D11</f>
-        <v>0.45</v>
+        <v>0.31568127025083792</v>
       </c>
       <c r="E19" s="40">
         <f t="shared" si="1"/>
-        <v>0.1193754192537093</v>
+        <v>8.37435199705273E-2</v>
       </c>
       <c r="F19" s="30">
         <f t="shared" si="2"/>
@@ -3066,11 +3169,11 @@
       </c>
       <c r="G19" s="41">
         <f>+(D19-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>1.7296363357464768E-2</v>
       </c>
       <c r="H19" s="33">
         <f t="shared" si="3"/>
-        <v>0.59231254132897648</v>
+        <v>0.45148258203094688</v>
       </c>
       <c r="I19" s="42">
         <f>+'1. Portfolio Detail'!E11</f>
@@ -3096,11 +3199,11 @@
       </c>
       <c r="D20" s="27">
         <f>+'1. Portfolio Detail'!D12</f>
-        <v>0.45</v>
+        <v>0.44498065115823748</v>
       </c>
       <c r="E20" s="40">
         <f t="shared" si="1"/>
-        <v>0.10456907136807402</v>
+        <v>0.10340269659639507</v>
       </c>
       <c r="F20" s="30">
         <f t="shared" si="2"/>
@@ -3108,11 +3211,11 @@
       </c>
       <c r="G20" s="41">
         <f>+(D20-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>4.9118008747968976E-6</v>
       </c>
       <c r="H20" s="33">
         <f t="shared" si="3"/>
-        <v>0.61983443515013292</v>
+        <v>0.61292855298758009</v>
       </c>
       <c r="I20" s="42">
         <f>+'1. Portfolio Detail'!E12</f>
@@ -3138,11 +3241,11 @@
       </c>
       <c r="D21" s="27">
         <f>+'1. Portfolio Detail'!D13</f>
-        <v>0.45</v>
+        <v>0.32100408780730172</v>
       </c>
       <c r="E21" s="40">
         <f t="shared" si="1"/>
-        <v>0.18954870264913046</v>
+        <v>0.13521312975320354</v>
       </c>
       <c r="F21" s="30">
         <f t="shared" si="2"/>
@@ -3150,11 +3253,11 @@
       </c>
       <c r="G21" s="41">
         <f>+(D21-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>1.5924628237504769E-2</v>
       </c>
       <c r="H21" s="33">
         <f t="shared" si="3"/>
-        <v>0.83169904884779511</v>
+        <v>0.63969616474945901</v>
       </c>
       <c r="I21" s="42">
         <f>+'1. Portfolio Detail'!E13</f>
@@ -3180,11 +3283,11 @@
       </c>
       <c r="D22" s="27">
         <f>+'1. Portfolio Detail'!D14</f>
-        <v>0.45</v>
+        <v>0.61231089109667203</v>
       </c>
       <c r="E22" s="40">
         <f t="shared" si="1"/>
-        <v>5.0665593287522175E-2</v>
+        <v>6.8940210164053925E-2</v>
       </c>
       <c r="F22" s="30">
         <f t="shared" si="2"/>
@@ -3192,11 +3295,11 @@
       </c>
       <c r="G22" s="41">
         <f>+(D22-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>2.726262693082266E-2</v>
       </c>
       <c r="H22" s="33">
         <f t="shared" si="3"/>
-        <v>0.46075268916933199</v>
+        <v>0.64960211305721338</v>
       </c>
       <c r="I22" s="42">
         <f>+'1. Portfolio Detail'!E14</f>
@@ -3222,11 +3325,11 @@
       </c>
       <c r="D23" s="27">
         <f>+'1. Portfolio Detail'!D15</f>
-        <v>0.45</v>
+        <v>0.66422676411838821</v>
       </c>
       <c r="E23" s="40">
         <f t="shared" si="1"/>
-        <v>9.799032493125244E-2</v>
+        <v>0.14463954765332274</v>
       </c>
       <c r="F23" s="30">
         <f t="shared" si="2"/>
@@ -3234,11 +3337,11 @@
       </c>
       <c r="G23" s="41">
         <f>+(D23-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>4.7101957811604964E-2</v>
       </c>
       <c r="H23" s="33">
         <f t="shared" si="3"/>
-        <v>0.4964451869483672</v>
+        <v>0.77235386303103803</v>
       </c>
       <c r="I23" s="42">
         <f>+'1. Portfolio Detail'!E15</f>
@@ -3264,11 +3367,11 @@
       </c>
       <c r="D24" s="27">
         <f>+'1. Portfolio Detail'!D16</f>
-        <v>0.45</v>
+        <v>0.23878214999183223</v>
       </c>
       <c r="E24" s="40">
         <f t="shared" si="1"/>
-        <v>8.6820678017758487E-3</v>
+        <v>4.6069395912953278E-3</v>
       </c>
       <c r="F24" s="30">
         <f t="shared" si="2"/>
@@ -3276,11 +3379,11 @@
       </c>
       <c r="G24" s="41">
         <f>+(D24-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>4.3436711965553369E-2</v>
       </c>
       <c r="H24" s="33">
         <f t="shared" si="3"/>
-        <v>7.9784081170192075E-2</v>
+        <v>5.6337243328528241E-2</v>
       </c>
       <c r="I24" s="42">
         <f>+'1. Portfolio Detail'!E16</f>
@@ -3306,11 +3409,11 @@
       </c>
       <c r="D25" s="27">
         <f>+'1. Portfolio Detail'!D17</f>
-        <v>0.45</v>
+        <v>0.6081541029929991</v>
       </c>
       <c r="E25" s="40">
         <f t="shared" si="1"/>
-        <v>4.030247146012958E-2</v>
+        <v>5.4466918620524558E-2</v>
       </c>
       <c r="F25" s="30">
         <f t="shared" si="2"/>
@@ -3318,11 +3421,11 @@
       </c>
       <c r="G25" s="41">
         <f>+(D25-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>2.5907218148954227E-2</v>
       </c>
       <c r="H25" s="33">
         <f t="shared" si="3"/>
-        <v>0.27095013342010099</v>
+        <v>0.37905858036509793</v>
       </c>
       <c r="I25" s="42">
         <f>+'1. Portfolio Detail'!E17</f>
@@ -3348,11 +3451,11 @@
       </c>
       <c r="D26" s="27">
         <f>+'1. Portfolio Detail'!D18</f>
-        <v>0.45</v>
+        <v>0.32507606539887124</v>
       </c>
       <c r="E26" s="40">
         <f t="shared" si="1"/>
-        <v>0.12902865889644963</v>
+        <v>9.3209175017224227E-2</v>
       </c>
       <c r="F26" s="30">
         <f t="shared" si="2"/>
@@ -3360,11 +3463,11 @@
       </c>
       <c r="G26" s="41">
         <f>+(D26-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>1.4913500555010636E-2</v>
       </c>
       <c r="H26" s="33">
         <f t="shared" si="3"/>
-        <v>0.55289703705906068</v>
+        <v>0.42809618728950732</v>
       </c>
       <c r="I26" s="42">
         <f>+'1. Portfolio Detail'!E18</f>
@@ -3390,11 +3493,11 @@
       </c>
       <c r="D27" s="27">
         <f>+'1. Portfolio Detail'!D19</f>
-        <v>0.45</v>
+        <v>0.57995192638740534</v>
       </c>
       <c r="E27" s="40">
         <f t="shared" si="1"/>
-        <v>0.10976499316776407</v>
+        <v>0.14146315386121144</v>
       </c>
       <c r="F27" s="30">
         <f t="shared" si="2"/>
@@ -3402,11 +3505,11 @@
       </c>
       <c r="G27" s="41">
         <f>+(D27-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>1.7623894518517199E-2</v>
       </c>
       <c r="H27" s="33">
         <f t="shared" si="3"/>
-        <v>0.72244085088154963</v>
+        <v>0.95569937739572486</v>
       </c>
       <c r="I27" s="42">
         <f>+'1. Portfolio Detail'!E19</f>
@@ -3432,11 +3535,11 @@
       </c>
       <c r="D28" s="27">
         <f>+'1. Portfolio Detail'!D20</f>
-        <v>0.45</v>
+        <v>0.56663508816453678</v>
       </c>
       <c r="E28" s="40">
         <f t="shared" si="1"/>
-        <v>5.6575115197850905E-2</v>
+        <v>7.1238767529006819E-2</v>
       </c>
       <c r="F28" s="30">
         <f t="shared" si="2"/>
@@ -3444,11 +3547,11 @@
       </c>
       <c r="G28" s="41">
         <f>+(D28-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>1.4265478531466506E-2</v>
       </c>
       <c r="H28" s="33">
         <f t="shared" si="3"/>
-        <v>0.24269504882977982</v>
+        <v>0.31267488510037117</v>
       </c>
       <c r="I28" s="42">
         <f>+'1. Portfolio Detail'!E20</f>
@@ -3474,11 +3577,11 @@
       </c>
       <c r="D29" s="27">
         <f>+'1. Portfolio Detail'!D21</f>
-        <v>0.45</v>
+        <v>0.41513870386821605</v>
       </c>
       <c r="E29" s="40">
         <f t="shared" si="1"/>
-        <v>3.9708517134034414E-2</v>
+        <v>3.6632316301226431E-2</v>
       </c>
       <c r="F29" s="30">
         <f t="shared" si="2"/>
@@ -3486,11 +3589,11 @@
       </c>
       <c r="G29" s="41">
         <f>+(D29-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>1.027728545977226E-3</v>
       </c>
       <c r="H29" s="33">
         <f t="shared" si="3"/>
-        <v>0.18645161752019929</v>
+        <v>0.17254259588466486</v>
       </c>
       <c r="I29" s="42">
         <f>+'1. Portfolio Detail'!E21</f>
@@ -3516,11 +3619,11 @@
       </c>
       <c r="D30" s="27">
         <f>+'1. Portfolio Detail'!D22</f>
-        <v>0.45</v>
+        <v>0.30486747389021596</v>
       </c>
       <c r="E30" s="40">
         <f t="shared" si="1"/>
-        <v>0.1079972588405573</v>
+        <v>7.3166336643974442E-2</v>
       </c>
       <c r="F30" s="30">
         <f t="shared" si="2"/>
@@ -3528,11 +3631,11 @@
       </c>
       <c r="G30" s="41">
         <f>+(D30-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>2.0257668230555144E-2</v>
       </c>
       <c r="H30" s="33">
         <f t="shared" si="3"/>
-        <v>0.5982354492683144</v>
+        <v>0.44858950187756919</v>
       </c>
       <c r="I30" s="42">
         <f>+'1. Portfolio Detail'!E22</f>
@@ -3558,11 +3661,11 @@
       </c>
       <c r="D31" s="27">
         <f>+'1. Portfolio Detail'!D23</f>
-        <v>0.45</v>
+        <v>0.403886053990132</v>
       </c>
       <c r="E31" s="40">
         <f t="shared" si="1"/>
-        <v>1.8687708260874649E-2</v>
+        <v>1.6772677216896563E-2</v>
       </c>
       <c r="F31" s="30">
         <f t="shared" si="2"/>
@@ -3570,11 +3673,11 @@
       </c>
       <c r="G31" s="41">
         <f>+(D31-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>1.8758302018183955E-3</v>
       </c>
       <c r="H31" s="33">
         <f t="shared" si="3"/>
-        <v>9.8882028859923629E-2</v>
+        <v>8.9275992497176659E-2</v>
       </c>
       <c r="I31" s="42">
         <f>+'1. Portfolio Detail'!E23</f>
@@ -3600,11 +3703,11 @@
       </c>
       <c r="D32" s="27">
         <f>+'1. Portfolio Detail'!D24</f>
-        <v>0.45</v>
+        <v>0.45547307616928723</v>
       </c>
       <c r="E32" s="40">
         <f t="shared" si="1"/>
-        <v>4.3845781360720225E-2</v>
+        <v>4.4379050918696081E-2</v>
       </c>
       <c r="F32" s="30">
         <f t="shared" si="2"/>
@@ -3612,11 +3715,11 @@
       </c>
       <c r="G32" s="41">
         <f>+(D32-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>6.8494935345148378E-5</v>
       </c>
       <c r="H32" s="33">
         <f t="shared" si="3"/>
-        <v>0.18879924464003403</v>
+        <v>0.19112874015039283</v>
       </c>
       <c r="I32" s="42">
         <f>+'1. Portfolio Detail'!E24</f>
@@ -3642,11 +3745,11 @@
       </c>
       <c r="D33" s="27">
         <f>+'1. Portfolio Detail'!D25</f>
-        <v>0.45</v>
+        <v>0.23046413256599207</v>
       </c>
       <c r="E33" s="40">
         <f t="shared" si="1"/>
-        <v>0.1078916500031423</v>
+        <v>5.5255901175750674E-2</v>
       </c>
       <c r="F33" s="30">
         <f t="shared" si="2"/>
@@ -3654,11 +3757,11 @@
       </c>
       <c r="G33" s="41">
         <f>+(D33-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>4.6973096581621999E-2</v>
       </c>
       <c r="H33" s="33">
         <f t="shared" si="3"/>
-        <v>0.46577886544064417</v>
+        <v>0.3315554411050271</v>
       </c>
       <c r="I33" s="42">
         <f>+'1. Portfolio Detail'!E25</f>
@@ -3684,11 +3787,11 @@
       </c>
       <c r="D34" s="27">
         <f>+'1. Portfolio Detail'!D26</f>
-        <v>0.45</v>
+        <v>0.49094368618115669</v>
       </c>
       <c r="E34" s="40">
         <f t="shared" si="1"/>
-        <v>3.5619149344379604E-2</v>
+        <v>3.885999217281523E-2</v>
       </c>
       <c r="F34" s="30">
         <f t="shared" si="2"/>
@@ -3696,11 +3799,11 @@
       </c>
       <c r="G34" s="41">
         <f>+(D34-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>1.913780473201252E-3</v>
       </c>
       <c r="H34" s="33">
         <f t="shared" si="3"/>
-        <v>0.34858863020059067</v>
+        <v>0.38182786177936234</v>
       </c>
       <c r="I34" s="42">
         <f>+'1. Portfolio Detail'!E26</f>
@@ -3726,11 +3829,11 @@
       </c>
       <c r="D35" s="27">
         <f>+'1. Portfolio Detail'!D27</f>
-        <v>0.45</v>
+        <v>0.25692441508306896</v>
       </c>
       <c r="E35" s="40">
         <f t="shared" si="1"/>
-        <v>3.4901813887206062E-2</v>
+        <v>1.9926951374019002E-2</v>
       </c>
       <c r="F35" s="30">
         <f t="shared" si="2"/>
@@ -3738,11 +3841,11 @@
       </c>
       <c r="G35" s="41">
         <f>+(D35-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>3.6203622117678344E-2</v>
       </c>
       <c r="H35" s="33">
         <f t="shared" si="3"/>
-        <v>0.14427014060990948</v>
+        <v>0.10355568867330427</v>
       </c>
       <c r="I35" s="42">
         <f>+'1. Portfolio Detail'!E27</f>
@@ -3768,11 +3871,11 @@
       </c>
       <c r="D36" s="27">
         <f>+'1. Portfolio Detail'!D28</f>
-        <v>0.45</v>
+        <v>0.6633103429721009</v>
       </c>
       <c r="E36" s="40">
         <f t="shared" si="1"/>
-        <v>5.2179384521491817E-2</v>
+        <v>7.6913612095608597E-2</v>
       </c>
       <c r="F36" s="30">
         <f t="shared" si="2"/>
@@ -3780,11 +3883,11 @@
       </c>
       <c r="G36" s="41">
         <f>+(D36-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>4.6705016142959167E-2</v>
       </c>
       <c r="H36" s="33">
         <f t="shared" si="3"/>
-        <v>0.44490002354234293</v>
+        <v>0.6901772345986783</v>
       </c>
       <c r="I36" s="42">
         <f>+'1. Portfolio Detail'!E28</f>
@@ -3810,11 +3913,11 @@
       </c>
       <c r="D37" s="27">
         <f>+'1. Portfolio Detail'!D29</f>
-        <v>0.45</v>
+        <v>0.24368356601692198</v>
       </c>
       <c r="E37" s="40">
         <f t="shared" si="1"/>
-        <v>4.3442548821872665E-2</v>
+        <v>2.3524967141729251E-2</v>
       </c>
       <c r="F37" s="30">
         <f t="shared" si="2"/>
@@ -3822,11 +3925,11 @@
       </c>
       <c r="G37" s="41">
         <f>+(D37-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>4.1417680960726934E-2</v>
       </c>
       <c r="H37" s="33">
         <f t="shared" si="3"/>
-        <v>0.27075498630425715</v>
+        <v>0.19203384188612624</v>
       </c>
       <c r="I37" s="42">
         <f>+'1. Portfolio Detail'!E29</f>
@@ -3852,11 +3955,11 @@
       </c>
       <c r="D38" s="27">
         <f>+'1. Portfolio Detail'!D30</f>
-        <v>0.45</v>
+        <v>0.56505132067971264</v>
       </c>
       <c r="E38" s="40">
         <f t="shared" si="1"/>
-        <v>0.1917986628986755</v>
+        <v>0.24083575061222132</v>
       </c>
       <c r="F38" s="30">
         <f t="shared" si="2"/>
@@ -3864,11 +3967,11 @@
       </c>
       <c r="G38" s="41">
         <f>+(D38-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>1.3889662243165252E-2</v>
       </c>
       <c r="H38" s="33">
         <f t="shared" si="3"/>
-        <v>0.81505928949588824</v>
+        <v>1.0466755439007351</v>
       </c>
       <c r="I38" s="42">
         <f>+'1. Portfolio Detail'!E30</f>
@@ -3894,11 +3997,11 @@
       </c>
       <c r="D39" s="27">
         <f>+'1. Portfolio Detail'!D31</f>
-        <v>0.45</v>
+        <v>0.4722905932909065</v>
       </c>
       <c r="E39" s="40">
         <f t="shared" si="1"/>
-        <v>0.11931386990353808</v>
+        <v>0.12522404089905784</v>
       </c>
       <c r="F39" s="30">
         <f t="shared" si="2"/>
@@ -3906,11 +4009,11 @@
       </c>
       <c r="G39" s="41">
         <f>+(D39-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>6.2969296803944618E-4</v>
       </c>
       <c r="H39" s="33">
         <f t="shared" si="3"/>
-        <v>0.48687942069820739</v>
+        <v>0.51176083798657701</v>
       </c>
       <c r="I39" s="42">
         <f>+'1. Portfolio Detail'!E31</f>
@@ -3936,11 +4039,11 @@
       </c>
       <c r="D40" s="27">
         <f>+'1. Portfolio Detail'!D32</f>
-        <v>0.45</v>
+        <v>0.63461637672113402</v>
       </c>
       <c r="E40" s="40">
         <f t="shared" si="1"/>
-        <v>0.14950230528648376</v>
+        <v>0.21083691398303367</v>
       </c>
       <c r="F40" s="30">
         <f t="shared" si="2"/>
@@ -3948,11 +4051,11 @@
       </c>
       <c r="G40" s="41">
         <f>+(D40-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>3.512605670720708E-2</v>
       </c>
       <c r="H40" s="33">
         <f t="shared" si="3"/>
-        <v>0.84196155460385302</v>
+        <v>1.2396466388784804</v>
       </c>
       <c r="I40" s="42">
         <f>+'1. Portfolio Detail'!E32</f>
@@ -3978,11 +4081,11 @@
       </c>
       <c r="D41" s="27">
         <f>+'1. Portfolio Detail'!D33</f>
-        <v>0.45</v>
+        <v>0.26427613870425681</v>
       </c>
       <c r="E41" s="40">
         <f t="shared" si="1"/>
-        <v>9.4443952669291592E-2</v>
+        <v>5.5465073634239935E-2</v>
       </c>
       <c r="F41" s="30">
         <f t="shared" si="2"/>
@@ -3990,11 +4093,11 @@
       </c>
       <c r="G41" s="41">
         <f>+(D41-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>3.3460008375085594E-2</v>
       </c>
       <c r="H41" s="33">
         <f t="shared" si="3"/>
-        <v>0.39680322016931036</v>
+        <v>0.2859994182699927</v>
       </c>
       <c r="I41" s="42">
         <f>+'1. Portfolio Detail'!E33</f>
@@ -4020,11 +4123,11 @@
       </c>
       <c r="D42" s="27">
         <f>+'1. Portfolio Detail'!D34</f>
-        <v>0.45</v>
+        <v>0.62262389971490506</v>
       </c>
       <c r="E42" s="40">
         <f t="shared" si="1"/>
-        <v>2.568497358950439E-2</v>
+        <v>3.5537952045270146E-2</v>
       </c>
       <c r="F42" s="30">
         <f t="shared" si="2"/>
@@ -4032,11 +4135,11 @@
       </c>
       <c r="G42" s="41">
         <f>+(D42-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>3.0774628908733705E-2</v>
       </c>
       <c r="H42" s="33">
         <f t="shared" si="3"/>
-        <v>0.22680182598261378</v>
+        <v>0.32617663009435038</v>
       </c>
       <c r="I42" s="42">
         <f>+'1. Portfolio Detail'!E34</f>
@@ -4062,11 +4165,11 @@
       </c>
       <c r="D43" s="27">
         <f>+'1. Portfolio Detail'!D35</f>
-        <v>0.45</v>
+        <v>0.68983689975407003</v>
       </c>
       <c r="E43" s="40">
         <f t="shared" si="1"/>
-        <v>2.7369392776447302E-2</v>
+        <v>4.1956482357901878E-2</v>
       </c>
       <c r="F43" s="30">
         <f t="shared" si="2"/>
@@ -4074,11 +4177,11 @@
       </c>
       <c r="G43" s="41">
         <f>+(D43-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>5.887416488830078E-2</v>
       </c>
       <c r="H43" s="33">
         <f t="shared" si="3"/>
-        <v>0.27001663582253105</v>
+        <v>0.43903438379911119</v>
       </c>
       <c r="I43" s="42">
         <f>+'1. Portfolio Detail'!E35</f>
@@ -4104,11 +4207,11 @@
       </c>
       <c r="D44" s="27">
         <f>+'1. Portfolio Detail'!D36</f>
-        <v>0.45</v>
+        <v>0.5300793531943534</v>
       </c>
       <c r="E44" s="40">
         <f t="shared" si="1"/>
-        <v>9.6100756978877599E-2</v>
+        <v>0.11320228244633596</v>
       </c>
       <c r="F44" s="30">
         <f t="shared" si="2"/>
@@ -4116,11 +4219,11 @@
       </c>
       <c r="G44" s="41">
         <f>+(D44-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>6.8694994788297999E-3</v>
       </c>
       <c r="H44" s="33">
         <f t="shared" si="3"/>
-        <v>0.54593142694535779</v>
+        <v>0.65113636075895409</v>
       </c>
       <c r="I44" s="42">
         <f>+'1. Portfolio Detail'!E36</f>
@@ -4146,11 +4249,11 @@
       </c>
       <c r="D45" s="27">
         <f>+'1. Portfolio Detail'!D37</f>
-        <v>0.45</v>
+        <v>0.59785757576352738</v>
       </c>
       <c r="E45" s="40">
         <f t="shared" si="1"/>
-        <v>0.2028017043580303</v>
+        <v>0.26943674517378574</v>
       </c>
       <c r="F45" s="30">
         <f t="shared" si="2"/>
@@ -4158,11 +4261,11 @@
       </c>
       <c r="G45" s="41">
         <f>+(D45-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>2.2698636370025865E-2</v>
       </c>
       <c r="H45" s="33">
         <f t="shared" si="3"/>
-        <v>0.89870974330628361</v>
+        <v>1.2332002501026864</v>
       </c>
       <c r="I45" s="42">
         <f>+'1. Portfolio Detail'!E37</f>
@@ -4188,11 +4291,11 @@
       </c>
       <c r="D46" s="27">
         <f>+'1. Portfolio Detail'!D38</f>
-        <v>0.45</v>
+        <v>0.23975885554750409</v>
       </c>
       <c r="E46" s="40">
         <f t="shared" si="1"/>
-        <v>5.4872613185400758E-2</v>
+        <v>2.9235988751627931E-2</v>
       </c>
       <c r="F46" s="30">
         <f t="shared" si="2"/>
@@ -4200,11 +4303,11 @@
       </c>
       <c r="G46" s="41">
         <f>+(D46-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>4.3030546212376238E-2</v>
       </c>
       <c r="H46" s="33">
         <f t="shared" si="3"/>
-        <v>0.23450524008514381</v>
+        <v>0.16714227202895535</v>
       </c>
       <c r="I46" s="42">
         <f>+'1. Portfolio Detail'!E38</f>
@@ -4230,11 +4333,11 @@
       </c>
       <c r="D47" s="27">
         <f>+'1. Portfolio Detail'!D39</f>
-        <v>0.45</v>
+        <v>0.59498578725052254</v>
       </c>
       <c r="E47" s="40">
         <f t="shared" si="1"/>
-        <v>0.21082687108793807</v>
+        <v>0.27875331526182501</v>
       </c>
       <c r="F47" s="30">
         <f t="shared" si="2"/>
@@ -4242,11 +4345,11 @@
       </c>
       <c r="G47" s="41">
         <f>+(D47-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>2.1841552397604044E-2</v>
       </c>
       <c r="H47" s="33">
         <f t="shared" si="3"/>
-        <v>0.88577146980912225</v>
+        <v>1.2087317983303956</v>
       </c>
       <c r="I47" s="42">
         <f>+'1. Portfolio Detail'!E39</f>
@@ -4272,11 +4375,11 @@
       </c>
       <c r="D48" s="27">
         <f>+'1. Portfolio Detail'!D40</f>
-        <v>0.45</v>
+        <v>0.60117178113189695</v>
       </c>
       <c r="E48" s="40">
         <f t="shared" si="1"/>
-        <v>0.14448091799107576</v>
+        <v>0.19301744624059233</v>
       </c>
       <c r="F48" s="30">
         <f t="shared" si="2"/>
@@ -4284,11 +4387,11 @@
       </c>
       <c r="G48" s="41">
         <f>+(D48-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>2.3708261105358237E-2</v>
       </c>
       <c r="H48" s="33">
         <f t="shared" si="3"/>
-        <v>0.78823055089341965</v>
+        <v>1.0881407473396634</v>
       </c>
       <c r="I48" s="42">
         <f>+'1. Portfolio Detail'!E40</f>
@@ -4314,11 +4417,11 @@
       </c>
       <c r="D49" s="27">
         <f>+'1. Portfolio Detail'!D41</f>
-        <v>0.45</v>
+        <v>0.64678015251833931</v>
       </c>
       <c r="E49" s="40">
         <f t="shared" si="1"/>
-        <v>0.18362033864435406</v>
+        <v>0.26391553474192098</v>
       </c>
       <c r="F49" s="30">
         <f t="shared" si="2"/>
@@ -4326,11 +4429,11 @@
       </c>
       <c r="G49" s="41">
         <f>+(D49-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>3.983347090836345E-2</v>
       </c>
       <c r="H49" s="33">
         <f t="shared" si="3"/>
-        <v>0.86181022806589858</v>
+        <v>1.2988594140296401</v>
       </c>
       <c r="I49" s="42">
         <f>+'1. Portfolio Detail'!E41</f>
@@ -4356,11 +4459,11 @@
       </c>
       <c r="D50" s="27">
         <f>+'1. Portfolio Detail'!D42</f>
-        <v>0.45</v>
+        <v>0.29802319506158736</v>
       </c>
       <c r="E50" s="40">
         <f t="shared" si="1"/>
-        <v>0.18532128395993611</v>
+        <v>0.12273342479701302</v>
       </c>
       <c r="F50" s="30">
         <f t="shared" si="2"/>
@@ -4368,11 +4471,11 @@
       </c>
       <c r="G50" s="41">
         <f>+(D50-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>2.2252797068406306E-2</v>
       </c>
       <c r="H50" s="33">
         <f t="shared" si="3"/>
-        <v>0.83126155973940441</v>
+        <v>0.61869468585403009</v>
       </c>
       <c r="I50" s="42">
         <f>+'1. Portfolio Detail'!E42</f>
@@ -4398,11 +4501,11 @@
       </c>
       <c r="D51" s="27">
         <f>+'1. Portfolio Detail'!D43</f>
-        <v>0.45</v>
+        <v>0.27041723174687338</v>
       </c>
       <c r="E51" s="40">
         <f t="shared" si="1"/>
-        <v>5.489135905359601E-2</v>
+        <v>3.298570969354913E-2</v>
       </c>
       <c r="F51" s="30">
         <f t="shared" si="2"/>
@@ -4410,11 +4513,11 @@
       </c>
       <c r="G51" s="41">
         <f>+(D51-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>3.1251054453526723E-2</v>
       </c>
       <c r="H51" s="33">
         <f t="shared" si="3"/>
-        <v>0.46618888255052998</v>
+        <v>0.33539017194792736</v>
       </c>
       <c r="I51" s="42">
         <f>+'1. Portfolio Detail'!E43</f>
@@ -4440,11 +4543,11 @@
       </c>
       <c r="D52" s="27">
         <f>+'1. Portfolio Detail'!D44</f>
-        <v>0.45</v>
+        <v>0.46055551204184697</v>
       </c>
       <c r="E52" s="40">
         <f t="shared" si="1"/>
-        <v>0.16886247690021322</v>
+        <v>0.17282343225207167</v>
       </c>
       <c r="F52" s="30">
         <f t="shared" si="2"/>
@@ -4452,11 +4555,11 @@
       </c>
       <c r="G52" s="41">
         <f>+(D52-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>1.7845226285133079E-4</v>
       </c>
       <c r="H52" s="33">
         <f t="shared" si="3"/>
-        <v>0.68835878359529812</v>
+        <v>0.70481952364411915</v>
       </c>
       <c r="I52" s="42">
         <f>+'1. Portfolio Detail'!E44</f>
@@ -4482,11 +4585,11 @@
       </c>
       <c r="D53" s="27">
         <f>+'1. Portfolio Detail'!D45</f>
-        <v>0.45</v>
+        <v>0.63229804231588249</v>
       </c>
       <c r="E53" s="40">
         <f t="shared" si="1"/>
-        <v>2.0568827523351738E-2</v>
+        <v>2.8901398612774101E-2</v>
       </c>
       <c r="F53" s="30">
         <f t="shared" si="2"/>
@@ -4494,11 +4597,11 @@
       </c>
       <c r="G53" s="41">
         <f>+(D53-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>3.4262429383306196E-2</v>
       </c>
       <c r="H53" s="33">
         <f t="shared" si="3"/>
-        <v>0.10580203746503664</v>
+        <v>0.15513324356642927</v>
       </c>
       <c r="I53" s="42">
         <f>+'1. Portfolio Detail'!E45</f>
@@ -4524,11 +4627,11 @@
       </c>
       <c r="D54" s="27">
         <f>+'1. Portfolio Detail'!D46</f>
-        <v>0.45</v>
+        <v>0.28290816055339119</v>
       </c>
       <c r="E54" s="40">
         <f t="shared" si="1"/>
-        <v>6.3190584221374441E-2</v>
+        <v>3.9726959880807086E-2</v>
       </c>
       <c r="F54" s="30">
         <f t="shared" si="2"/>
@@ -4536,11 +4639,11 @@
       </c>
       <c r="G54" s="41">
         <f>+(D54-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>2.6990793018385906E-2</v>
       </c>
       <c r="H54" s="33">
         <f t="shared" si="3"/>
-        <v>0.31812236752513806</v>
+        <v>0.23242349607660245</v>
       </c>
       <c r="I54" s="42">
         <f>+'1. Portfolio Detail'!E46</f>
@@ -4566,11 +4669,11 @@
       </c>
       <c r="D55" s="27">
         <f>+'1. Portfolio Detail'!D47</f>
-        <v>0.45</v>
+        <v>0.44450404250639997</v>
       </c>
       <c r="E55" s="40">
         <f t="shared" si="1"/>
-        <v>8.7877953882165558E-2</v>
+        <v>8.6804679439585725E-2</v>
       </c>
       <c r="F55" s="30">
         <f t="shared" si="2"/>
@@ -4578,11 +4681,11 @@
       </c>
       <c r="G55" s="41">
         <f>+(D55-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>7.2515324476106112E-6</v>
       </c>
       <c r="H55" s="33">
         <f t="shared" si="3"/>
-        <v>0.42818387542431374</v>
+        <v>0.42296245174626218</v>
       </c>
       <c r="I55" s="42">
         <f>+'1. Portfolio Detail'!E47</f>
@@ -4608,11 +4711,11 @@
       </c>
       <c r="D56" s="27">
         <f>+'1. Portfolio Detail'!D48</f>
-        <v>0.45</v>
+        <v>0.31914538221676392</v>
       </c>
       <c r="E56" s="40">
         <f t="shared" si="1"/>
-        <v>9.271564742823539E-2</v>
+        <v>6.5755046079908688E-2</v>
       </c>
       <c r="F56" s="30">
         <f t="shared" si="2"/>
@@ -4620,11 +4723,11 @@
       </c>
       <c r="G56" s="41">
         <f>+(D56-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>1.6397193630172585E-2</v>
       </c>
       <c r="H56" s="33">
         <f t="shared" si="3"/>
-        <v>0.44351198947404036</v>
+        <v>0.33994378672384695</v>
       </c>
       <c r="I56" s="42">
         <f>+'1. Portfolio Detail'!E48</f>
@@ -4650,11 +4753,11 @@
       </c>
       <c r="D57" s="27">
         <f>+'1. Portfolio Detail'!D49</f>
-        <v>0.45</v>
+        <v>0.29875486333017853</v>
       </c>
       <c r="E57" s="40">
         <f t="shared" si="1"/>
-        <v>0.15814144131841107</v>
+        <v>0.10499005486204299</v>
       </c>
       <c r="F57" s="30">
         <f t="shared" si="2"/>
@@ -4662,11 +4765,11 @@
       </c>
       <c r="G57" s="41">
         <f>+(D57-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>2.203504106019033E-2</v>
       </c>
       <c r="H57" s="33">
         <f t="shared" si="3"/>
-        <v>0.74025487944037383</v>
+        <v>0.55125084010853398</v>
       </c>
       <c r="I57" s="42">
         <f>+'1. Portfolio Detail'!E49</f>
@@ -4692,11 +4795,11 @@
       </c>
       <c r="D58" s="27">
         <f>+'1. Portfolio Detail'!D50</f>
-        <v>0.45</v>
+        <v>0.68617424011340833</v>
       </c>
       <c r="E58" s="40">
         <f t="shared" si="1"/>
-        <v>0.14385806941087731</v>
+        <v>0.21935933658264595</v>
       </c>
       <c r="F58" s="30">
         <f t="shared" si="2"/>
@@ -4704,11 +4807,11 @@
       </c>
       <c r="G58" s="41">
         <f>+(D58-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>5.7110164564647077E-2</v>
       </c>
       <c r="H58" s="33">
         <f t="shared" si="3"/>
-        <v>0.65522002643245703</v>
+        <v>1.0607144404405824</v>
       </c>
       <c r="I58" s="42">
         <f>+'1. Portfolio Detail'!E50</f>
@@ -4734,11 +4837,11 @@
       </c>
       <c r="D59" s="27">
         <f>+'1. Portfolio Detail'!D51</f>
-        <v>0.45</v>
+        <v>0.47821276883639796</v>
       </c>
       <c r="E59" s="40">
         <f t="shared" si="1"/>
-        <v>0.21958202176456237</v>
+        <v>0.23334872581050128</v>
       </c>
       <c r="F59" s="30">
         <f t="shared" si="2"/>
@@ -4746,11 +4849,11 @@
       </c>
       <c r="G59" s="41">
         <f>+(D59-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>9.6198353265125234E-4</v>
       </c>
       <c r="H59" s="33">
         <f t="shared" si="3"/>
-        <v>0.88364588445093428</v>
+        <v>0.94114079316651356</v>
       </c>
       <c r="I59" s="42">
         <f>+'1. Portfolio Detail'!E51</f>
@@ -4776,11 +4879,11 @@
       </c>
       <c r="D60" s="27">
         <f>+'1. Portfolio Detail'!D52</f>
-        <v>0.45</v>
+        <v>0.37728556210490194</v>
       </c>
       <c r="E60" s="40">
         <f t="shared" si="1"/>
-        <v>3.5004547687925963E-2</v>
+        <v>2.9348245445926652E-2</v>
       </c>
       <c r="F60" s="30">
         <f t="shared" si="2"/>
@@ -4788,11 +4891,11 @@
       </c>
       <c r="G60" s="41">
         <f>+(D60-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>4.8875964894678006E-3</v>
       </c>
       <c r="H60" s="33">
         <f t="shared" si="3"/>
-        <v>0.23523442763604341</v>
+        <v>0.20065455691402342</v>
       </c>
       <c r="I60" s="42">
         <f>+'1. Portfolio Detail'!E52</f>
@@ -4818,11 +4921,11 @@
       </c>
       <c r="D61" s="27">
         <f>+'1. Portfolio Detail'!D53</f>
-        <v>0.45</v>
+        <v>0.61104187246048813</v>
       </c>
       <c r="E61" s="40">
         <f t="shared" si="1"/>
-        <v>0.11511669354610747</v>
+        <v>0.15631359994638599</v>
       </c>
       <c r="F61" s="30">
         <f t="shared" si="2"/>
@@ -4830,11 +4933,11 @@
       </c>
       <c r="G61" s="41">
         <f>+(D61-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>2.6845171899547115E-2</v>
       </c>
       <c r="H61" s="33">
         <f t="shared" si="3"/>
-        <v>0.65500490655227861</v>
+        <v>0.92178454347916994</v>
       </c>
       <c r="I61" s="42">
         <f>+'1. Portfolio Detail'!E53</f>
@@ -4860,11 +4963,11 @@
       </c>
       <c r="D62" s="27">
         <f>+'1. Portfolio Detail'!D54</f>
-        <v>0.45</v>
+        <v>0.24488742906452443</v>
       </c>
       <c r="E62" s="40">
         <f t="shared" si="1"/>
-        <v>3.789780617203499E-2</v>
+        <v>2.0623769601456256E-2</v>
       </c>
       <c r="F62" s="30">
         <f t="shared" si="2"/>
@@ -4872,11 +4975,11 @@
       </c>
       <c r="G62" s="41">
         <f>+(D62-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>4.0929125859226055E-2</v>
       </c>
       <c r="H62" s="33">
         <f t="shared" si="3"/>
-        <v>0.22244471402277707</v>
+        <v>0.15794095213349868</v>
       </c>
       <c r="I62" s="42">
         <f>+'1. Portfolio Detail'!E54</f>
@@ -4902,11 +5005,11 @@
       </c>
       <c r="D63" s="27">
         <f>+'1. Portfolio Detail'!D55</f>
-        <v>0.45</v>
+        <v>0.25464974174436694</v>
       </c>
       <c r="E63" s="40">
         <f t="shared" si="1"/>
-        <v>0.11905784543652145</v>
+        <v>6.7373443540113209E-2</v>
       </c>
       <c r="F63" s="30">
         <f t="shared" si="2"/>
@@ -4914,11 +5017,11 @@
       </c>
       <c r="G63" s="41">
         <f>+(D63-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>3.7074411796586264E-2</v>
       </c>
       <c r="H63" s="33">
         <f t="shared" si="3"/>
-        <v>0.6534409200450304</v>
+        <v>0.46637144956829318</v>
       </c>
       <c r="I63" s="42">
         <f>+'1. Portfolio Detail'!E55</f>
@@ -4944,11 +5047,11 @@
       </c>
       <c r="D64" s="27">
         <f>+'1. Portfolio Detail'!D56</f>
-        <v>0.45</v>
+        <v>0.30861886504360347</v>
       </c>
       <c r="E64" s="40">
         <f t="shared" si="1"/>
-        <v>1.1956750343285827E-2</v>
+        <v>8.2001749345657505E-3</v>
       </c>
       <c r="F64" s="30">
         <f t="shared" si="2"/>
@@ -4956,11 +5059,11 @@
       </c>
       <c r="G64" s="41">
         <f>+(D64-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>1.9203874395189779E-2</v>
       </c>
       <c r="H64" s="33">
         <f t="shared" si="3"/>
-        <v>7.558816345671153E-2</v>
+        <v>5.6945311338526386E-2</v>
       </c>
       <c r="I64" s="42">
         <f>+'1. Portfolio Detail'!E56</f>
@@ -4986,11 +5089,11 @@
       </c>
       <c r="D65" s="27">
         <f>+'1. Portfolio Detail'!D57</f>
-        <v>0.45</v>
+        <v>0.34290007437103986</v>
       </c>
       <c r="E65" s="40">
         <f t="shared" si="1"/>
-        <v>0.19587560329565629</v>
+        <v>0.14925724208345076</v>
       </c>
       <c r="F65" s="30">
         <f t="shared" si="2"/>
@@ -4998,11 +5101,11 @@
       </c>
       <c r="G65" s="41">
         <f>+(D65-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>1.0877829810263908E-2</v>
       </c>
       <c r="H65" s="33">
         <f t="shared" si="3"/>
-        <v>0.82527878938319232</v>
+        <v>0.65887437772771285</v>
       </c>
       <c r="I65" s="42">
         <f>+'1. Portfolio Detail'!E57</f>
@@ -5028,11 +5131,11 @@
       </c>
       <c r="D66" s="27">
         <f>+'1. Portfolio Detail'!D58</f>
-        <v>0.45</v>
+        <v>0.33976200731732742</v>
       </c>
       <c r="E66" s="40">
         <f t="shared" si="1"/>
-        <v>5.4824232297813906E-2</v>
+        <v>4.1393758255859343E-2</v>
       </c>
       <c r="F66" s="30">
         <f t="shared" si="2"/>
@@ -5040,11 +5143,11 @@
       </c>
       <c r="G66" s="41">
         <f>+(D66-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>1.1542258199116561E-2</v>
       </c>
       <c r="H66" s="33">
         <f t="shared" si="3"/>
-        <v>0.22709398634543956</v>
+        <v>0.18030548867422139</v>
       </c>
       <c r="I66" s="42">
         <f>+'1. Portfolio Detail'!E58</f>
@@ -5070,11 +5173,11 @@
       </c>
       <c r="D67" s="27">
         <f>+'1. Portfolio Detail'!D59</f>
-        <v>0.45</v>
+        <v>0.3213960702055253</v>
       </c>
       <c r="E67" s="40">
         <f t="shared" si="1"/>
-        <v>0.17217049822064751</v>
+        <v>0.12296649229654111</v>
       </c>
       <c r="F67" s="30">
         <f t="shared" si="2"/>
@@ -5082,11 +5185,11 @@
       </c>
       <c r="G67" s="41">
         <f>+(D67-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>1.5825851157962645E-2</v>
       </c>
       <c r="H67" s="33">
         <f t="shared" si="3"/>
-        <v>0.8492405628124976</v>
+        <v>0.65312365157495733</v>
       </c>
       <c r="I67" s="42">
         <f>+'1. Portfolio Detail'!E59</f>
@@ -5112,11 +5215,11 @@
       </c>
       <c r="D68" s="27">
         <f>+'1. Portfolio Detail'!D60</f>
-        <v>0.45</v>
+        <v>0.4221139839134509</v>
       </c>
       <c r="E68" s="40">
         <f t="shared" si="1"/>
-        <v>0.10474527777960967</v>
+        <v>9.8254325554826896E-2</v>
       </c>
       <c r="F68" s="30">
         <f t="shared" si="2"/>
@@ -5124,11 +5227,11 @@
       </c>
       <c r="G68" s="41">
         <f>+(D68-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>6.2915315413970667E-4</v>
       </c>
       <c r="H68" s="33">
         <f t="shared" si="3"/>
-        <v>0.60598091776390994</v>
+        <v>0.56946153772447028</v>
       </c>
       <c r="I68" s="42">
         <f>+'1. Portfolio Detail'!E60</f>
@@ -5154,11 +5257,11 @@
       </c>
       <c r="D69" s="27">
         <f>+'1. Portfolio Detail'!D61</f>
-        <v>0.45</v>
+        <v>0.2117527587759801</v>
       </c>
       <c r="E69" s="40">
         <f t="shared" si="1"/>
-        <v>1.2243059074178371E-2</v>
+        <v>5.7611145218101484E-3</v>
       </c>
       <c r="F69" s="30">
         <f t="shared" si="2"/>
@@ -5166,11 +5269,11 @@
       </c>
       <c r="G69" s="41">
         <f>+(D69-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>5.5433948092877473E-2</v>
       </c>
       <c r="H69" s="33">
         <f t="shared" si="3"/>
-        <v>0.11236582236419911</v>
+        <v>7.9329477497764131E-2</v>
       </c>
       <c r="I69" s="42">
         <f>+'1. Portfolio Detail'!E61</f>
@@ -5196,11 +5299,11 @@
       </c>
       <c r="D70" s="27">
         <f>+'1. Portfolio Detail'!D62</f>
-        <v>0.45</v>
+        <v>0.68773675939844758</v>
       </c>
       <c r="E70" s="40">
         <f t="shared" si="1"/>
-        <v>2.9446707973977866E-2</v>
+        <v>4.5003518926613251E-2</v>
       </c>
       <c r="F70" s="30">
         <f t="shared" si="2"/>
@@ -5208,11 +5311,11 @@
       </c>
       <c r="G70" s="41">
         <f>+(D70-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>5.7859419406819157E-2</v>
       </c>
       <c r="H70" s="33">
         <f t="shared" si="3"/>
-        <v>0.28433380177106682</v>
+        <v>0.46062978992703119</v>
       </c>
       <c r="I70" s="42">
         <f>+'1. Portfolio Detail'!E62</f>
@@ -5238,11 +5341,11 @@
       </c>
       <c r="D71" s="27">
         <f>+'1. Portfolio Detail'!D63</f>
-        <v>0.45</v>
+        <v>0.39674587505405601</v>
       </c>
       <c r="E71" s="40">
         <f t="shared" si="1"/>
-        <v>4.0141785174203588E-2</v>
+        <v>3.5391305967047412E-2</v>
       </c>
       <c r="F71" s="30">
         <f t="shared" si="2"/>
@@ -5250,11 +5353,11 @@
       </c>
       <c r="G71" s="41">
         <f>+(D71-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>2.5453068729635936E-3</v>
       </c>
       <c r="H71" s="33">
         <f t="shared" si="3"/>
-        <v>0.27107088347062452</v>
+        <v>0.2409582314198154</v>
       </c>
       <c r="I71" s="42">
         <f>+'1. Portfolio Detail'!E63</f>
@@ -5280,11 +5383,11 @@
       </c>
       <c r="D72" s="27">
         <f>+'1. Portfolio Detail'!D64</f>
-        <v>0.45</v>
+        <v>0.42137740161448733</v>
       </c>
       <c r="E72" s="40">
         <f t="shared" si="1"/>
-        <v>0.10817439225324819</v>
+        <v>0.10129387628644455</v>
       </c>
       <c r="F72" s="30">
         <f t="shared" si="2"/>
@@ -5292,11 +5395,11 @@
       </c>
       <c r="G72" s="41">
         <f>+(D72-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>6.6664698555534525E-4</v>
       </c>
       <c r="H72" s="33">
         <f t="shared" si="3"/>
-        <v>0.69867089032745933</v>
+        <v>0.65548778207673219</v>
       </c>
       <c r="I72" s="42">
         <f>+'1. Portfolio Detail'!E64</f>
@@ -5322,11 +5425,11 @@
       </c>
       <c r="D73" s="27">
         <f>+'1. Portfolio Detail'!D65</f>
-        <v>0.45</v>
+        <v>0.29064867434225439</v>
       </c>
       <c r="E73" s="40">
         <f t="shared" si="1"/>
-        <v>0.11209140552120681</v>
+        <v>7.2398263155330697E-2</v>
       </c>
       <c r="F73" s="30">
         <f t="shared" si="2"/>
@@ -5334,11 +5437,11 @@
       </c>
       <c r="G73" s="41">
         <f>+(D73-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>2.4507349919516887E-2</v>
       </c>
       <c r="H73" s="33">
         <f t="shared" si="3"/>
-        <v>0.7251233081168581</v>
+        <v>0.53338946827466815</v>
       </c>
       <c r="I73" s="42">
         <f>+'1. Portfolio Detail'!E65</f>
@@ -5364,11 +5467,11 @@
       </c>
       <c r="D74" s="27">
         <f>+'1. Portfolio Detail'!D66</f>
-        <v>0.45</v>
+        <v>0.54348701272375433</v>
       </c>
       <c r="E74" s="40">
         <f t="shared" si="1"/>
-        <v>7.4353118680812605E-3</v>
+        <v>8.9799898574510258E-3</v>
       </c>
       <c r="F74" s="30">
         <f t="shared" si="2"/>
@@ -5376,11 +5479,11 @@
       </c>
       <c r="G74" s="41">
         <f>+(D74-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>9.271783985907292E-3</v>
       </c>
       <c r="H74" s="33">
         <f t="shared" si="3"/>
-        <v>6.7608637929378684E-2</v>
+        <v>8.2941162909489136E-2</v>
       </c>
       <c r="I74" s="42">
         <f>+'1. Portfolio Detail'!E66</f>
@@ -5406,11 +5509,11 @@
       </c>
       <c r="D75" s="27">
         <f>+'1. Portfolio Detail'!D67</f>
-        <v>0.45</v>
+        <v>0.60731939550287373</v>
       </c>
       <c r="E75" s="40">
         <f t="shared" ref="E75:E109" si="6">+B75*C75*D75</f>
-        <v>8.2693214092567108E-2</v>
+        <v>0.11160265065530572</v>
       </c>
       <c r="F75" s="30">
         <f t="shared" ref="F75:F109" si="7">+C75*(1-C75)</f>
@@ -5418,11 +5521,11 @@
       </c>
       <c r="G75" s="41">
         <f>+(D75-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>2.5639210535490713E-2</v>
       </c>
       <c r="H75" s="33">
         <f t="shared" ref="H75:H109" si="8">+B75*(SQRT((C75*G75)+((D75^2)*F75)))</f>
-        <v>0.33244015318491621</v>
+        <v>0.46492490293011152</v>
       </c>
       <c r="I75" s="42">
         <f>+'1. Portfolio Detail'!E67</f>
@@ -5448,11 +5551,11 @@
       </c>
       <c r="D76" s="27">
         <f>+'1. Portfolio Detail'!D68</f>
-        <v>0.45</v>
+        <v>0.54733973209912379</v>
       </c>
       <c r="E76" s="40">
         <f t="shared" si="6"/>
-        <v>0.17645173091610375</v>
+        <v>0.21462009584010422</v>
       </c>
       <c r="F76" s="30">
         <f t="shared" si="7"/>
@@ -5460,11 +5563,11 @@
       </c>
       <c r="G76" s="41">
         <f>+(D76-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>1.0028584925468331E-2</v>
       </c>
       <c r="H76" s="33">
         <f t="shared" si="8"/>
-        <v>0.83931987526083851</v>
+        <v>1.0385626160552071</v>
       </c>
       <c r="I76" s="42">
         <f>+'1. Portfolio Detail'!E68</f>
@@ -5490,11 +5593,11 @@
       </c>
       <c r="D77" s="27">
         <f>+'1. Portfolio Detail'!D69</f>
-        <v>0.45</v>
+        <v>0.31161773195781539</v>
       </c>
       <c r="E77" s="40">
         <f t="shared" si="6"/>
-        <v>9.4199824003893387E-2</v>
+        <v>6.52318566820414E-2</v>
       </c>
       <c r="F77" s="30">
         <f t="shared" si="7"/>
@@ -5502,11 +5605,11 @@
       </c>
       <c r="G77" s="41">
         <f>+(D77-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>1.8381713373066048E-2</v>
       </c>
       <c r="H77" s="33">
         <f t="shared" si="8"/>
-        <v>0.64940662065798738</v>
+        <v>0.49124413041822229</v>
       </c>
       <c r="I77" s="42">
         <f>+'1. Portfolio Detail'!E69</f>
@@ -5532,11 +5635,11 @@
       </c>
       <c r="D78" s="27">
         <f>+'1. Portfolio Detail'!D70</f>
-        <v>0.45</v>
+        <v>0.65960207770955959</v>
       </c>
       <c r="E78" s="40">
         <f t="shared" si="6"/>
-        <v>3.3480210498998145E-2</v>
+        <v>4.9074703127316856E-2</v>
       </c>
       <c r="F78" s="30">
         <f t="shared" si="7"/>
@@ -5544,11 +5647,11 @@
       </c>
       <c r="G78" s="41">
         <f>+(D78-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>4.5115955497718171E-2</v>
       </c>
       <c r="H78" s="33">
         <f t="shared" si="8"/>
-        <v>0.13753505765255128</v>
+        <v>0.21237992975655665</v>
       </c>
       <c r="I78" s="42">
         <f>+'1. Portfolio Detail'!E70</f>
@@ -5574,11 +5677,11 @@
       </c>
       <c r="D79" s="27">
         <f>+'1. Portfolio Detail'!D71</f>
-        <v>0.45</v>
+        <v>0.44582121139090425</v>
       </c>
       <c r="E79" s="40">
         <f t="shared" si="6"/>
-        <v>1.0618257800838258E-2</v>
+        <v>1.0519654568068068E-2</v>
       </c>
       <c r="F79" s="30">
         <f t="shared" si="7"/>
@@ -5586,11 +5689,11 @@
       </c>
       <c r="G79" s="41">
         <f>+(D79-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>1.8925451864171723E-6</v>
       </c>
       <c r="H79" s="33">
         <f t="shared" si="8"/>
-        <v>8.8460654025885474E-2</v>
+        <v>8.7639614231546106E-2</v>
       </c>
       <c r="I79" s="42">
         <f>+'1. Portfolio Detail'!E71</f>
@@ -5616,11 +5719,11 @@
       </c>
       <c r="D80" s="27">
         <f>+'1. Portfolio Detail'!D72</f>
-        <v>0.45</v>
+        <v>0.46300614450734534</v>
       </c>
       <c r="E80" s="40">
         <f t="shared" si="6"/>
-        <v>4.3968592391560313E-2</v>
+        <v>4.523939653918075E-2</v>
       </c>
       <c r="F80" s="30">
         <f t="shared" si="7"/>
@@ -5628,11 +5731,11 @@
       </c>
       <c r="G80" s="41">
         <f>+(D80-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>2.4993191267759794E-4</v>
       </c>
       <c r="H80" s="33">
         <f t="shared" si="8"/>
-        <v>0.20514269316491188</v>
+        <v>0.21120049240755212</v>
       </c>
       <c r="I80" s="42">
         <f>+'1. Portfolio Detail'!E72</f>
@@ -5658,11 +5761,11 @@
       </c>
       <c r="D81" s="27">
         <f>+'1. Portfolio Detail'!D73</f>
-        <v>0.45</v>
+        <v>0.36469003508983466</v>
       </c>
       <c r="E81" s="40">
         <f t="shared" si="6"/>
-        <v>7.6265616459066737E-2</v>
+        <v>6.180735631689982E-2</v>
       </c>
       <c r="F81" s="30">
         <f t="shared" si="7"/>
@@ -5670,11 +5773,11 @@
       </c>
       <c r="G81" s="41">
         <f>+(D81-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>6.8073843188802179E-3</v>
       </c>
       <c r="H81" s="33">
         <f t="shared" si="8"/>
-        <v>0.39615659129854414</v>
+        <v>0.32946486360142774</v>
       </c>
       <c r="I81" s="42">
         <f>+'1. Portfolio Detail'!E73</f>
@@ -5700,11 +5803,11 @@
       </c>
       <c r="D82" s="27">
         <f>+'1. Portfolio Detail'!D74</f>
-        <v>0.45</v>
+        <v>0.44641921040529908</v>
       </c>
       <c r="E82" s="40">
         <f t="shared" si="6"/>
-        <v>9.547941161206859E-2</v>
+        <v>9.4719652315160455E-2</v>
       </c>
       <c r="F82" s="30">
         <f t="shared" si="7"/>
@@ -5712,11 +5815,11 @@
       </c>
       <c r="G82" s="41">
         <f>+(D82-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>6.0481582482896037E-7</v>
       </c>
       <c r="H82" s="33">
         <f t="shared" si="8"/>
-        <v>0.46790485043227614</v>
+        <v>0.46418232007800975</v>
       </c>
       <c r="I82" s="42">
         <f>+'1. Portfolio Detail'!E74</f>
@@ -5742,11 +5845,11 @@
       </c>
       <c r="D83" s="27">
         <f>+'1. Portfolio Detail'!D75</f>
-        <v>0.45</v>
+        <v>0.4899126991343784</v>
       </c>
       <c r="E83" s="40">
         <f t="shared" si="6"/>
-        <v>3.4921113929358726E-2</v>
+        <v>3.8018438182025049E-2</v>
       </c>
       <c r="F83" s="30">
         <f t="shared" si="7"/>
@@ -5754,11 +5857,11 @@
       </c>
       <c r="G83" s="41">
         <f>+(D83-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>1.8246386872230699E-3</v>
       </c>
       <c r="H83" s="33">
         <f t="shared" si="8"/>
-        <v>0.31320063609338583</v>
+        <v>0.34228962797757084</v>
       </c>
       <c r="I83" s="42">
         <f>+'1. Portfolio Detail'!E75</f>
@@ -5784,11 +5887,11 @@
       </c>
       <c r="D84" s="27">
         <f>+'1. Portfolio Detail'!D76</f>
-        <v>0.45</v>
+        <v>0.6128320693544691</v>
       </c>
       <c r="E84" s="40">
         <f t="shared" si="6"/>
-        <v>2.046818776832789E-2</v>
+        <v>2.7874581924444919E-2</v>
       </c>
       <c r="F84" s="30">
         <f t="shared" si="7"/>
@@ -5796,11 +5899,11 @@
       </c>
       <c r="G84" s="41">
         <f>+(D84-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>2.7435006192170288E-2</v>
       </c>
       <c r="H84" s="33">
         <f t="shared" si="8"/>
-        <v>9.5771883508556768E-2</v>
+        <v>0.13531663971641686</v>
       </c>
       <c r="I84" s="42">
         <f>+'1. Portfolio Detail'!E76</f>
@@ -5826,11 +5929,11 @@
       </c>
       <c r="D85" s="27">
         <f>+'1. Portfolio Detail'!D77</f>
-        <v>0.45</v>
+        <v>0.55158045878683415</v>
       </c>
       <c r="E85" s="40">
         <f t="shared" si="6"/>
-        <v>0.18338466965432851</v>
+        <v>0.22478088938312565</v>
       </c>
       <c r="F85" s="30">
         <f t="shared" si="7"/>
@@ -5838,11 +5941,11 @@
       </c>
       <c r="G85" s="41">
         <f>+(D85-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>1.0895925369376882E-2</v>
       </c>
       <c r="H85" s="33">
         <f t="shared" si="8"/>
-        <v>0.90764284815772345</v>
+        <v>1.1330743225697708</v>
       </c>
       <c r="I85" s="42">
         <f>+'1. Portfolio Detail'!E77</f>
@@ -5868,11 +5971,11 @@
       </c>
       <c r="D86" s="27">
         <f>+'1. Portfolio Detail'!D78</f>
-        <v>0.45</v>
+        <v>0.22903941923322435</v>
       </c>
       <c r="E86" s="40">
         <f t="shared" si="6"/>
-        <v>0.18358329057293066</v>
+        <v>9.3439578341662902E-2</v>
       </c>
       <c r="F86" s="30">
         <f t="shared" si="7"/>
@@ -5880,11 +5983,11 @@
       </c>
       <c r="G86" s="41">
         <f>+(D86-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>4.7592690543489323E-2</v>
       </c>
       <c r="H86" s="33">
         <f t="shared" si="8"/>
-        <v>0.77232404191856363</v>
+        <v>0.55012149688140322</v>
       </c>
       <c r="I86" s="42">
         <f>+'1. Portfolio Detail'!E78</f>
@@ -5910,11 +6013,11 @@
       </c>
       <c r="D87" s="27">
         <f>+'1. Portfolio Detail'!D79</f>
-        <v>0.45</v>
+        <v>0.2246684297905045</v>
       </c>
       <c r="E87" s="40">
         <f t="shared" si="6"/>
-        <v>5.3477133776351556E-2</v>
+        <v>2.6699163722732566E-2</v>
       </c>
       <c r="F87" s="30">
         <f t="shared" si="7"/>
@@ -5922,11 +6025,11 @@
       </c>
       <c r="G87" s="41">
         <f>+(D87-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>4.9518924265489608E-2</v>
       </c>
       <c r="H87" s="33">
         <f t="shared" si="8"/>
-        <v>0.51012455984642613</v>
+        <v>0.3594438438572678</v>
       </c>
       <c r="I87" s="42">
         <f>+'1. Portfolio Detail'!E79</f>
@@ -5952,11 +6055,11 @@
       </c>
       <c r="D88" s="27">
         <f>+'1. Portfolio Detail'!D80</f>
-        <v>0.45</v>
+        <v>0.69029541274852779</v>
       </c>
       <c r="E88" s="40">
         <f t="shared" si="6"/>
-        <v>7.2925273211499567E-2</v>
+        <v>0.11186662571406944</v>
       </c>
       <c r="F88" s="30">
         <f t="shared" si="7"/>
@@ -5964,11 +6067,11 @@
       </c>
       <c r="G88" s="41">
         <f>+(D88-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>5.9096882299513702E-2</v>
       </c>
       <c r="H88" s="33">
         <f t="shared" si="8"/>
-        <v>0.45571460783238288</v>
+        <v>0.7421903080785125</v>
       </c>
       <c r="I88" s="42">
         <f>+'1. Portfolio Detail'!E80</f>
@@ -5994,11 +6097,11 @@
       </c>
       <c r="D89" s="27">
         <f>+'1. Portfolio Detail'!D81</f>
-        <v>0.45</v>
+        <v>0.33517539806233332</v>
       </c>
       <c r="E89" s="40">
         <f t="shared" si="6"/>
-        <v>6.7728657441563839E-2</v>
+        <v>5.0446621596007934E-2</v>
       </c>
       <c r="F89" s="30">
         <f t="shared" si="7"/>
@@ -6006,11 +6109,11 @@
       </c>
       <c r="G89" s="41">
         <f>+(D89-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>1.2548819016558846E-2</v>
       </c>
       <c r="H89" s="33">
         <f t="shared" si="8"/>
-        <v>0.35219359561915603</v>
+        <v>0.27710255481191859</v>
       </c>
       <c r="I89" s="42">
         <f>+'1. Portfolio Detail'!E81</f>
@@ -6036,11 +6139,11 @@
       </c>
       <c r="D90" s="27">
         <f>+'1. Portfolio Detail'!D82</f>
-        <v>0.45</v>
+        <v>0.65168796537799534</v>
       </c>
       <c r="E90" s="40">
         <f t="shared" si="6"/>
-        <v>9.1053510526686143E-2</v>
+        <v>0.13186328225702215</v>
       </c>
       <c r="F90" s="30">
         <f t="shared" si="7"/>
@@ -6048,11 +6151,11 @@
       </c>
       <c r="G90" s="41">
         <f>+(D90-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>4.1816591949103518E-2</v>
       </c>
       <c r="H90" s="33">
         <f t="shared" si="8"/>
-        <v>0.54694502416089119</v>
+        <v>0.83119358060592918</v>
       </c>
       <c r="I90" s="42">
         <f>+'1. Portfolio Detail'!E82</f>
@@ -6078,11 +6181,11 @@
       </c>
       <c r="D91" s="27">
         <f>+'1. Portfolio Detail'!D83</f>
-        <v>0.45</v>
+        <v>0.65605080246849312</v>
       </c>
       <c r="E91" s="40">
         <f t="shared" si="6"/>
-        <v>1.3607863327335211E-2</v>
+        <v>1.9838777012844099E-2</v>
       </c>
       <c r="F91" s="30">
         <f t="shared" si="7"/>
@@ -6090,11 +6193,11 @@
       </c>
       <c r="G91" s="41">
         <f>+(D91-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>4.3619948623421043E-2</v>
       </c>
       <c r="H91" s="33">
         <f t="shared" si="8"/>
-        <v>9.8266728943060211E-2</v>
+        <v>0.15047915993076</v>
       </c>
       <c r="I91" s="42">
         <f>+'1. Portfolio Detail'!E83</f>
@@ -6120,11 +6223,11 @@
       </c>
       <c r="D92" s="27">
         <f>+'1. Portfolio Detail'!D84</f>
-        <v>0.45</v>
+        <v>0.34616762559222491</v>
       </c>
       <c r="E92" s="40">
         <f t="shared" si="6"/>
-        <v>0.10001932346532834</v>
+        <v>7.6941003816296483E-2</v>
       </c>
       <c r="F92" s="30">
         <f t="shared" si="7"/>
@@ -6132,11 +6235,11 @@
       </c>
       <c r="G92" s="41">
         <f>+(D92-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>1.0206916199504019E-2</v>
       </c>
       <c r="H92" s="33">
         <f t="shared" si="8"/>
-        <v>0.54206455937863007</v>
+        <v>0.43496541149365109</v>
       </c>
       <c r="I92" s="42">
         <f>+'1. Portfolio Detail'!E84</f>
@@ -6162,11 +6265,11 @@
       </c>
       <c r="D93" s="27">
         <f>+'1. Portfolio Detail'!D85</f>
-        <v>0.45</v>
+        <v>0.66212402721431252</v>
       </c>
       <c r="E93" s="40">
         <f t="shared" si="6"/>
-        <v>2.3230862719368035E-2</v>
+        <v>3.4181583065357332E-2</v>
       </c>
       <c r="F93" s="30">
         <f t="shared" si="7"/>
@@ -6174,11 +6277,11 @@
       </c>
       <c r="G93" s="41">
         <f>+(D93-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>4.6193665944753881E-2</v>
       </c>
       <c r="H93" s="33">
         <f t="shared" si="8"/>
-        <v>0.15908465525268253</v>
+        <v>0.24634813341842329</v>
       </c>
       <c r="I93" s="42">
         <f>+'1. Portfolio Detail'!E85</f>
@@ -6204,11 +6307,11 @@
       </c>
       <c r="D94" s="27">
         <f>+'1. Portfolio Detail'!D86</f>
-        <v>0.45</v>
+        <v>0.34106067816254171</v>
       </c>
       <c r="E94" s="40">
         <f t="shared" si="6"/>
-        <v>9.9766388327597974E-2</v>
+        <v>7.5614204579640118E-2</v>
       </c>
       <c r="F94" s="30">
         <f t="shared" si="7"/>
@@ -6216,11 +6319,11 @@
       </c>
       <c r="G94" s="41">
         <f>+(D94-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>1.1264899594729899E-2</v>
       </c>
       <c r="H94" s="33">
         <f t="shared" si="8"/>
-        <v>0.43102175322843433</v>
+        <v>0.34293761854643945</v>
       </c>
       <c r="I94" s="42">
         <f>+'1. Portfolio Detail'!E86</f>
@@ -6246,11 +6349,11 @@
       </c>
       <c r="D95" s="27">
         <f>+'1. Portfolio Detail'!D87</f>
-        <v>0.45</v>
+        <v>0.42962505681095808</v>
       </c>
       <c r="E95" s="40">
         <f t="shared" si="6"/>
-        <v>9.1626846388121991E-2</v>
+        <v>8.7478197966457422E-2</v>
       </c>
       <c r="F95" s="30">
         <f t="shared" si="7"/>
@@ -6258,11 +6361,11 @@
       </c>
       <c r="G95" s="41">
         <f>+(D95-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>3.0877000563591945E-4</v>
       </c>
       <c r="H95" s="33">
         <f t="shared" si="8"/>
-        <v>0.37026930292556753</v>
+        <v>0.35381802480844166</v>
       </c>
       <c r="I95" s="42">
         <f>+'1. Portfolio Detail'!E87</f>
@@ -6288,11 +6391,11 @@
       </c>
       <c r="D96" s="27">
         <f>+'1. Portfolio Detail'!D88</f>
-        <v>0.45</v>
+        <v>0.42656939327163235</v>
       </c>
       <c r="E96" s="40">
         <f t="shared" si="6"/>
-        <v>3.6204759787888716E-2</v>
+        <v>3.4319649813921958E-2</v>
       </c>
       <c r="F96" s="30">
         <f t="shared" si="7"/>
@@ -6300,11 +6403,11 @@
       </c>
       <c r="G96" s="41">
         <f>+(D96-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>4.2549442423786787E-4</v>
       </c>
       <c r="H96" s="33">
         <f t="shared" si="8"/>
-        <v>0.20583761379087745</v>
+        <v>0.19535510615413743</v>
       </c>
       <c r="I96" s="42">
         <f>+'1. Portfolio Detail'!E88</f>
@@ -6330,11 +6433,11 @@
       </c>
       <c r="D97" s="27">
         <f>+'1. Portfolio Detail'!D89</f>
-        <v>0.45</v>
+        <v>0.24529615989531661</v>
       </c>
       <c r="E97" s="40">
         <f t="shared" si="6"/>
-        <v>0.16125832150531952</v>
+        <v>8.7902326703153844E-2</v>
       </c>
       <c r="F97" s="30">
         <f t="shared" si="7"/>
@@ -6342,11 +6445,11 @@
       </c>
       <c r="G97" s="41">
         <f>+(D97-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>4.0763912676117037E-2</v>
       </c>
       <c r="H97" s="33">
         <f t="shared" si="8"/>
-        <v>0.64997610287295415</v>
+        <v>0.46455375853823944</v>
       </c>
       <c r="I97" s="42">
         <f>+'1. Portfolio Detail'!E89</f>
@@ -6372,11 +6475,11 @@
       </c>
       <c r="D98" s="27">
         <f>+'1. Portfolio Detail'!D90</f>
-        <v>0.45</v>
+        <v>0.47841175237598021</v>
       </c>
       <c r="E98" s="40">
         <f t="shared" si="6"/>
-        <v>9.6482482746219983E-2</v>
+        <v>0.10257411920934306</v>
       </c>
       <c r="F98" s="30">
         <f t="shared" si="7"/>
@@ -6384,11 +6487,11 @@
       </c>
       <c r="G98" s="41">
         <f>+(D98-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>9.7436641806276252E-4</v>
       </c>
       <c r="H98" s="33">
         <f t="shared" si="8"/>
-        <v>0.40988665784034789</v>
+        <v>0.43674362111988257</v>
       </c>
       <c r="I98" s="42">
         <f>+'1. Portfolio Detail'!E90</f>
@@ -6414,11 +6517,11 @@
       </c>
       <c r="D99" s="27">
         <f>+'1. Portfolio Detail'!D91</f>
-        <v>0.45</v>
+        <v>0.5404282094171039</v>
       </c>
       <c r="E99" s="40">
         <f t="shared" si="6"/>
-        <v>5.0246991653427026E-2</v>
+        <v>6.0344203839683849E-2</v>
       </c>
       <c r="F99" s="30">
         <f t="shared" si="7"/>
@@ -6426,11 +6529,11 @@
       </c>
       <c r="G99" s="41">
         <f>+(D99-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>8.6920752910745434E-3</v>
       </c>
       <c r="H99" s="33">
         <f t="shared" si="8"/>
-        <v>0.44416875009424373</v>
+        <v>0.54140469117223256</v>
       </c>
       <c r="I99" s="42">
         <f>+'1. Portfolio Detail'!E91</f>
@@ -6456,11 +6559,11 @@
       </c>
       <c r="D100" s="27">
         <f>+'1. Portfolio Detail'!D92</f>
-        <v>0.45</v>
+        <v>0.36883666172921803</v>
       </c>
       <c r="E100" s="40">
         <f t="shared" si="6"/>
-        <v>3.0471639108758653E-2</v>
+        <v>2.4975683658426725E-2</v>
       </c>
       <c r="F100" s="30">
         <f t="shared" si="7"/>
@@ -6468,11 +6571,11 @@
       </c>
       <c r="G100" s="41">
         <f>+(D100-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>6.1403284249480538E-3</v>
       </c>
       <c r="H100" s="33">
         <f t="shared" si="8"/>
-        <v>0.26463080263328703</v>
+        <v>0.22180568866432057</v>
       </c>
       <c r="I100" s="42">
         <f>+'1. Portfolio Detail'!E92</f>
@@ -6498,11 +6601,11 @@
       </c>
       <c r="D101" s="27">
         <f>+'1. Portfolio Detail'!D93</f>
-        <v>0.45</v>
+        <v>0.69111517152179447</v>
       </c>
       <c r="E101" s="40">
         <f t="shared" si="6"/>
-        <v>0.16069098823729772</v>
+        <v>0.2467910664391704</v>
       </c>
       <c r="F101" s="30">
         <f t="shared" si="7"/>
@@ -6510,11 +6613,11 @@
       </c>
       <c r="G101" s="41">
         <f>+(D101-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>5.9496118565632167E-2</v>
       </c>
       <c r="H101" s="33">
         <f t="shared" si="8"/>
-        <v>0.70157714757273193</v>
+        <v>1.1459438023238546</v>
       </c>
       <c r="I101" s="42">
         <f>+'1. Portfolio Detail'!E93</f>
@@ -6540,11 +6643,11 @@
       </c>
       <c r="D102" s="27">
         <f>+'1. Portfolio Detail'!D94</f>
-        <v>0.45</v>
+        <v>0.60933843535586474</v>
       </c>
       <c r="E102" s="40">
         <f t="shared" si="6"/>
-        <v>8.323562145993911E-2</v>
+        <v>0.11270814076949408</v>
       </c>
       <c r="F102" s="30">
         <f t="shared" si="7"/>
@@ -6552,11 +6655,11 @@
       </c>
       <c r="G102" s="41">
         <f>+(D102-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>2.6289874418766439E-2</v>
       </c>
       <c r="H102" s="33">
         <f t="shared" si="8"/>
-        <v>0.36125448054383141</v>
+        <v>0.50707905726971469</v>
       </c>
       <c r="I102" s="42">
         <f>+'1. Portfolio Detail'!E94</f>
@@ -6582,11 +6685,11 @@
       </c>
       <c r="D103" s="27">
         <f>+'1. Portfolio Detail'!D95</f>
-        <v>0.45</v>
+        <v>0.47619805291810435</v>
       </c>
       <c r="E103" s="40">
         <f t="shared" si="6"/>
-        <v>0.10906554027728065</v>
+        <v>0.11541510649000473</v>
       </c>
       <c r="F103" s="30">
         <f t="shared" si="7"/>
@@ -6594,11 +6697,11 @@
       </c>
       <c r="G103" s="41">
         <f>+(D103-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>8.4106632168563995E-4</v>
       </c>
       <c r="H103" s="33">
         <f t="shared" si="8"/>
-        <v>0.43895651573945293</v>
+        <v>0.46542535547273223</v>
       </c>
       <c r="I103" s="42">
         <f>+'1. Portfolio Detail'!E95</f>
@@ -6624,11 +6727,11 @@
       </c>
       <c r="D104" s="27">
         <f>+'1. Portfolio Detail'!D96</f>
-        <v>0.45</v>
+        <v>0.44802418381057518</v>
       </c>
       <c r="E104" s="40">
         <f t="shared" si="6"/>
-        <v>3.1459777313740715E-2</v>
+        <v>3.1321646786335852E-2</v>
       </c>
       <c r="F104" s="30">
         <f t="shared" si="7"/>
@@ -6636,11 +6739,11 @@
       </c>
       <c r="G104" s="41">
         <f>+(D104-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>6.8438284564527625E-7</v>
       </c>
       <c r="H104" s="33">
         <f t="shared" si="8"/>
-        <v>0.17145070267419091</v>
+        <v>0.17069821441924735</v>
       </c>
       <c r="I104" s="42">
         <f>+'1. Portfolio Detail'!E96</f>
@@ -6666,11 +6769,11 @@
       </c>
       <c r="D105" s="27">
         <f>+'1. Portfolio Detail'!D97</f>
-        <v>0.45</v>
+        <v>0.27749968198730535</v>
       </c>
       <c r="E105" s="40">
         <f t="shared" si="6"/>
-        <v>0.22452860315923995</v>
+        <v>0.13845914660831771</v>
       </c>
       <c r="F105" s="30">
         <f t="shared" si="7"/>
@@ -6678,11 +6781,11 @@
       </c>
       <c r="G105" s="41">
         <f>+(D105-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>2.8797149013042408E-2</v>
       </c>
       <c r="H105" s="33">
         <f t="shared" si="8"/>
-        <v>0.95449940022030111</v>
+        <v>0.69511807546856752</v>
       </c>
       <c r="I105" s="42">
         <f>+'1. Portfolio Detail'!E97</f>
@@ -6708,11 +6811,11 @@
       </c>
       <c r="D106" s="27">
         <f>+'1. Portfolio Detail'!D98</f>
-        <v>0.45</v>
+        <v>0.42073014950101695</v>
       </c>
       <c r="E106" s="40">
         <f t="shared" si="6"/>
-        <v>0.20825969401335673</v>
+        <v>0.19471362710505694</v>
       </c>
       <c r="F106" s="30">
         <f t="shared" si="7"/>
@@ -6720,11 +6823,11 @@
       </c>
       <c r="G106" s="41">
         <f>+(D106-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>7.0048938290156678E-4</v>
       </c>
       <c r="H106" s="33">
         <f t="shared" si="8"/>
-        <v>0.96187509778366043</v>
+        <v>0.90117167832694922</v>
       </c>
       <c r="I106" s="42">
         <f>+'1. Portfolio Detail'!E98</f>
@@ -6750,11 +6853,11 @@
       </c>
       <c r="D107" s="27">
         <f>+'1. Portfolio Detail'!D99</f>
-        <v>0.45</v>
+        <v>0.67895755809370006</v>
       </c>
       <c r="E107" s="40">
         <f t="shared" si="6"/>
-        <v>7.5509471067315939E-2</v>
+        <v>0.11392828019735939</v>
       </c>
       <c r="F107" s="30">
         <f t="shared" si="7"/>
@@ -6762,11 +6865,11 @@
       </c>
       <c r="G107" s="41">
         <f>+(D107-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>5.3712998253579752E-2</v>
       </c>
       <c r="H107" s="33">
         <f t="shared" si="8"/>
-        <v>0.3253373418301127</v>
+        <v>0.52013281756997276</v>
       </c>
       <c r="I107" s="42">
         <f>+'1. Portfolio Detail'!E99</f>
@@ -6792,11 +6895,11 @@
       </c>
       <c r="D108" s="27">
         <f>+'1. Portfolio Detail'!D100</f>
-        <v>0.45</v>
+        <v>0.62216876669906396</v>
       </c>
       <c r="E108" s="40">
         <f t="shared" si="6"/>
-        <v>0.14446046020077105</v>
+        <v>0.19973063635531763</v>
       </c>
       <c r="F108" s="30">
         <f t="shared" si="7"/>
@@ -6804,11 +6907,11 @@
       </c>
       <c r="G108" s="41">
         <f>+(D108-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>3.0615150824529539E-2</v>
       </c>
       <c r="H108" s="33">
         <f t="shared" si="8"/>
-        <v>0.82664861070614915</v>
+        <v>1.1885868075871895</v>
       </c>
       <c r="I108" s="42">
         <f>+'1. Portfolio Detail'!E100</f>
@@ -6834,11 +6937,11 @@
       </c>
       <c r="D109" s="28">
         <f>+'1. Portfolio Detail'!D101</f>
-        <v>0.45</v>
+        <v>0.62765712114478645</v>
       </c>
       <c r="E109" s="44">
         <f t="shared" si="6"/>
-        <v>8.6400706325198945E-2</v>
+        <v>0.1205111524376678</v>
       </c>
       <c r="F109" s="31">
         <f t="shared" si="7"/>
@@ -6846,11 +6949,11 @@
       </c>
       <c r="G109" s="45">
         <f>+(D109-'2. Working sheet'!$C$5)^2</f>
-        <v>1.5099290763995929E-31</v>
+        <v>3.2565888000123777E-2</v>
       </c>
       <c r="H109" s="34">
         <f t="shared" si="8"/>
-        <v>0.39414564040830408</v>
+        <v>0.57307153017914203</v>
       </c>
       <c r="I109" s="46">
         <f>+'1. Portfolio Detail'!E101</f>
@@ -6876,7 +6979,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{443BC9B1-A601-4B0E-AE9A-5BB3C3E23157}">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.5546875" bestFit="1" customWidth="1"/>
@@ -6887,7 +6990,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F1" s="6"/>
     </row>
@@ -6910,11 +7013,11 @@
         <v>3000</v>
       </c>
       <c r="C3" s="5">
-        <v>0.16999999999999996</v>
+        <v>0.1</v>
       </c>
       <c r="D3">
         <f>+C3*B3</f>
-        <v>509.99999999999989</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -6925,11 +7028,11 @@
         <v>2000</v>
       </c>
       <c r="C4" s="5">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="D4">
         <f>+C4*B4</f>
-        <v>240</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6939,24 +7042,24 @@
       </c>
       <c r="D5" s="7">
         <f>SUM(D3:D4)</f>
-        <v>749.99999999999989</v>
+        <v>480</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="D6" s="1">
         <f>+D5/B5</f>
-        <v>0.14999999999999997</v>
+        <v>9.6000000000000002E-2</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D7" s="1"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" s="4">
         <v>0.99970000000000003</v>
@@ -6965,7 +7068,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" s="2">
         <f>+_xlfn.NORM.S.INV(B8)</f>
@@ -6975,17 +7078,17 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B10" s="6">
         <f>+'2. Working sheet'!H8*B9</f>
-        <v>160.39237478305242</v>
+        <v>169.41630768279137</v>
       </c>
       <c r="D10" s="1"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -7014,73 +7117,91 @@
       </c>
       <c r="B16" s="2">
         <f>+'2. Working sheet'!$E$8</f>
-        <v>9.1356316019026256</v>
+        <v>9.007556776357184</v>
       </c>
       <c r="C16" s="2"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="B17" s="6">
         <f>+B14-B15-B16</f>
-        <v>7.1044470098083377</v>
+        <v>7.2325218353537792</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="B18" s="6">
-        <f>'3. Decision Maker'!B10</f>
-        <v>160.39237478305242</v>
+        <f>+B17*0.3</f>
+        <v>2.1697565506061336</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="6">
+        <f>+B17-B18</f>
+        <v>5.0627652847476456</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="6">
+        <f>'3. Decision Maker'!B10</f>
+        <v>169.41630768279137</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="1">
-        <f>+B17/B18</f>
-        <v>4.4294169342014238E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E20" s="4"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E21" s="2"/>
+      <c r="B21" s="60">
+        <f>+B19/B20</f>
+        <v>2.988357705343794E-2</v>
+      </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" s="6"/>
+      <c r="E22" s="4"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="1">
-        <f>+B19-D6</f>
-        <v>-0.10570583065798572</v>
-      </c>
+      <c r="E23" s="2"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" t="str">
-        <f>+IF(B19&gt;D6,"Yes","No")</f>
-        <v>No</v>
-      </c>
+      <c r="A24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="6"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>19</v>
-      </c>
-      <c r="B25" t="str">
-        <f>+IF(B24="Yes","Yes","No")</f>
+        <v>25</v>
+      </c>
+      <c r="B25" s="1">
+        <f>+B21-D6</f>
+        <v>-6.6116422946562059E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" t="str">
+        <f>+IF(B21&gt;D6,"Yes","No")</f>
+        <v>No</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" t="str">
+        <f>+IF(B26="Yes","Yes","No")</f>
         <v>No</v>
       </c>
     </row>
